--- a/Ministry_of_Economy_and_Trade.xlsx
+++ b/Ministry_of_Economy_and_Trade.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -802,6 +802,1520 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>الأخبار | البساط في الدوحة… التعافي مدخلًا للاستثمار، والإصلاح أساسًا للثقة | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/البساط-في-الدوحة…-التعافي-مدخلًا-للاستثمار،-والإصلاح-أساسًا-للثقة</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>البساط في الدوحة… التعافي مدخلًا للاستثمار، والإصلاح أساسًا للثقة
+*البساط في الدوحة… التعافي مدخلًا للاستثمار، والإصلاح أساسًا للثقة*
+تعزيز ثقة المستثمرين وإعادة وصل لبنان بالأسواق العربية والدولية شكّلا محور مشاركة وزير الاقتصاد والتجارة الدكتور عامر البساط في المنتدى العالمي للاستثمار، الذي استضافته الدوحة بين ٢٤ و٢٦ تشرين الأول ٢٠٢٦. ومثّل البساط لبنان بدعوة من دولة قطر ومؤتمر الأمم المتحدة للتجارة والتنمية، وعقد لقاءات مع مسؤولين وقيادات اقتصادية لبحث فرص التعاون والاستثمار.
+وحمل البساط إلى نقاشات المنتدى أولويات واضحة ترتكز على تعزيز ثقة المستثمرين بالإصلاحات، وتطوير سياسات المنافسة والتجارة، وبناء شراكات تواكب التعافي الاقتصادي. وعرض الفرص التي تفتحها عودة طرق التجارة مع سوريا والعراق والأردن ودول الخليج أمام المنتجات اللبنانية والاستثمارات.
+وفي جلسة نظّمتها منظمة التجارة العالمية، تناول عودة لبنان إلى سلاسل القيمة الإقليمية والعالمية، ودور مسار الانضمام إلى المنظمة والانفتاح في قطاع الخدمات في توسيع فرصه التجارية. كما شارك في نقاشات حول الاستثمار من أجل السلام وتمويل التنمية بمشاركة القطاع الخاص.
+وكان تعزيز الشراكة الاقتصادية مع قطر في صلب لقاءاته مع وزيرة الدولة للتعاون الدولي الدكتورة مريم المسند، ووزير الدولة لشؤون التجارة الخارجية الدكتور أحمد السيد، ورئيس غرفة قطر الشيخ خليفة بن جاسم آل ثاني، والرئيس التنفيذي لوكالة ترويج الاستثمار في قطر الشيخ علي الوليد آل ثاني. وبحث معهم فرص التعاون والاستثمار وإعادة تنشيط التواصل بين قطاعَي الأعمال في البلدين. والتقى أيضًا السيد عبدالله الدردري من برنامج الأمم المتحدة الإنمائي.
+وامتدّ هذا التواصل إلى رجال أعمال لبنانيين في قطر ورؤساء مجموعات اقتصادية قطرية بارزة، وجّه إليهم البساط دعوات لزيارة لبنان واستكشاف فرص الاستثمار فيه، بهدف ترجمة الاهتمام بلبنان إلى شراكات اقتصادية.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:08:19.380998+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>الأخبار | البساط: نحمل إلى العراق مقترحات عملية لمعالجة عوائق التصدير | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/البساط-نحمل-إلى-العراق-مقترحات-عملية-لمعالجة-عوائق-التصدير</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>البساط: نحمل إلى العراق مقترحات عملية لمعالجة عوائق التصدير
+*البساط: نحمل إلى العراق مقترحات عملية لمعالجة عوائق التصدير*
+تحديات التصدير معروفة، والمطلوب حلول عملية تفتح الطريق أمام المنتج اللبناني. بهذه الأولوية، عقد وزير الاقتصاد والتجارة الدكتور عامر البساط اجتماعًا مع ممثلي القطاع الخاص والإدارات المعنية، تحضيرًا لزيارته إلى العراق يومي ٨ و٩ تشرين الثاني، على رأس وفد يضم ممثلين عن القطاعين العام والخاص.
+وشدّد البساط على أن الزيارة تنطلق من الصعوبات التي يواجهها الصناعيون والمزارعون والمصدّرون، وتحمل ملفات أساسية للبحث مع المسؤولين العراقيين. فالهدف هو تحويل الفرص المتاحة للدخول إلى السوق العراقي إلى صادرات فعلية، عبر معالجة العوائق الجمركية وغير الجمركية لتسهيل دخول المنتجات اللبنانية.
+ستحمل البعثة الممثّلة للقطاعين العام والخاص أولويات محددة، تشمل توضيح الوضع القانوني لاتفاقية التجارة الحرة الثنائية بين لبنان والعراق الموقعة في عام ٢٠٠٢ لإعادة تفعيلها، وتحديد السلع الحسّاسة للطرفين لبلورة بروتوكول ثنائي ينظّم معاملتها. كما ستبحث تحديث اتفاقية الاعتراف المتبادل بين البلدين عبر المجلس اللبناني للاعتماد (COLIBAC) والجهاز المركزي للتقييس والسيطرة النوعية في العراق (COSQC)، والعمل على تطوير بروتوكول لقبول نتائج الفحوصات الصناعية والغذائية الصادرة عن المختبرات اللبنانية المعترف بها، بالتنسيق مع الوزارات المختصة. وبالتوازي، تتواصل المحادثات مع الجانب السوري لمعالجة صعوبات عبور البضائع اللبنانية إلى الدول العربية، باعتبار أن تسهيل الوصول إلى الأسواق يتطلّب أيضًا معالجة العقبات اللتي يواجهها المصدرون عبر النقل البري.
+وتأتي هذه التحضيرات ضمن جهود حكومية مشتركة مبنية على نتائج الإتصالات والزيارات السابقة، ومنها زيارة وزير الزراعة إلى العراق، مع إشراك القطاع الخاص في تحديد الأولويات والمقترحات التي يحملها الوفد.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:08:23.595492+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>الأخبار | البساط في إطلاق حملة بيروت ماراثون: حيوية لبيروت وفرصة للاقتصاد والسياحة | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/البساط-في-إطلاق-حملة-بيروت-ماراثون-حيوية-لبيروت-وفرصة-للاقتصاد-والسياحة</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>البساط في إطلاق حملة بيروت ماراثون: حيوية لبيروت وفرصة للاقتصاد والسياحة
+*البساط في إطلاق حملة بيروت ماراثون: حيوية لبيروت وفرصة للاقتصاد والسياحة*
+استضاف وزير الاقتصاد والتجارة الدكتور عامر البساط، الثلاثاء ٢٠ تشرين الأول ٢٠٢٦ في مقرّ الوزارة، لقاء إطلاق حملة بيروت ماراثون ٢٠٢٦، بمشاركة رئيسة الجمعية مي الخليل وفريق عملها، وعدد من كبار ممثّلي القطاع الخاص.
+وأكّد البساط أن الماراثون يحمل إلى بيروت أجواءً من الفرح والحيوية تحتاجها المدينة، إلى جانب أثره الاقتصادي والسياحي، إذ يسهم استقطاب المشاركين والزوّار في تنشيط الحركة في الفنادق والمطاعم والأسواق.
+وأشار إلى أن السياحة الرياضية تمثّل مجالًا واعدًا يستطيع لبنان التميّز فيه، بفضل الكفاءات والخبرات اللبنانية في تنظيم أحداث تستقطب مشاركين من لبنان والخارج.
+وفي هذا الإطار، جاءت مشاركة ممثّلي القطاع الخاص لتعزيز التنسيق بين الوزارة والجمعية والقطاعات المعنية، حيث دعا البساط إلى تعاون عملي لإنجاح الماراثون وتوسيع أثره الاقتصادي والسياحي.
+وتضمّن اللقاء كلمة للخليل، تلتها عروض قدّمها فريق الجمعية تناولت برنامج نسخة هذا العام والتحضيرات الجارية لتنظيمها. 
+حول الكاتب: الوزير
+كان لوريم إيبسوم ولايزال المعيار للنص الشكلي منذ القرن الخامس عشر عندما قامت مطبعة مجهولة برص مجموعة من الأحرف بشكل عشوائي أخذتها من نص. لوريم إيبسوم هو ببساطة نص شكلي، بمعنى أن الغاية هي الشكل وليس المحتوى. ويُستخدم في صناعات المطابع ودور النشر. كان لوريم إيبسوم ولايزال المعيار للنص الشكلي منذ القرن الخامس عشر عندما قامت مطبعة مجهولة برص مجموعة من الأحرف بشكل عشوائي أخذتها من نص، لتكوّن كتيّب بمثابة دليل أو مرجع شكلي لهذه الأحرف.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:08:27.939936+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>الأخبار | مدير عام وزارة الاقتصاد والتجارة يشارك في افتتاح الجناح اللبناني في معرض SIAL Paris الدولي | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/مدير-عام-وزارة-الاقتصاد-والتجارة-يشارك-في-افتتاح-الجناح-اللبناني-في-معرض-sial-paris-الدولي</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>الجمهورية اللبنانية 
+مدير عام وزارة الاقتصاد والتجارة يشارك في افتتاح الجناح اللبناني في معرض SIAL Paris الدولي
+شارك المدير العام لوزارة الاقتصاد والتجارة، الدكتور محمد أبو حيدر، اليوم في افتتاح الجناح اللبناني في معرض SIAL Paris الدولي للصناعات الغذائية في باريس، بحضور وزير الصناعة جو عيسى الخوري، وسفير لبنان في فرنسا ربيع الشاعر، والمدير العام للزراعة المهندس لويس لحود، والمدير العام للصناعة عادل شباب، إلى جانب ممثلين عن نقابة الصناعات الغذائية والقطاع الخاص والشركة المنظمة وعدد من الفعاليات.
+وأكدت المشاركة أهمية تعزيز حضور المنتجات والصناعات الغذائية اللبنانية في المعارض الدولية المتخصصة، لما توفره من فرص للترويج للمنتج الوطني، وفتح أسواق جديدة أمام الصادرات اللبنانية، وبناء شراكات تجارية مع المستوردين والموزعين الدوليين.
+وتندرج هذه المشاركة في إطار دعم وزارة الاقتصاد والتجارة للقطاع الإنتاجي اللبناني، وتعزيز تنافسية المؤسسات الوطنية، وتوسيع نطاق وصول المنتجات اللبنانية إلى الأسواق الخارجية، بما يسهم في تنمية الصادرات وخلق فرص اقتصادية جديدة للمؤسسات الصغيرة والمتوسطة.
+وتؤكد الوزارة أن المشاركة الفاعلة في المعارض الدولية تشكّل أداة أساسية للتسويق للمنتج اللبناني وإبراز جودته وقدرته على المنافسة، بما يعزز حضور لبنان على خريطة التجارة العالمية.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:08:31.982197+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>الأخبار | وزارة الاقتصاد والتجارة تدفع بالتعاون التجاري مع سوريا إلى مرحلة جديدة | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/وزارة-الاقتصاد-والتجارة-تدفع-بالتعاون-التجاري-مع-سوريا-إلى-مرحلة-جديدة</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>وزارة الاقتصاد والتجارة تدفع بالتعاون التجاري مع سوريا إلى مرحلة جديدة
+*وزارة الاقتصاد والتجارة تدفع بالتعاون التجاري مع سوريا إلى مرحلة جديدة*
+استكمالاً للاجتماعات الوزارية التي عُقدت منذ أيار بين وزير الاقتصاد اللبناني الدكتور عامر بساط ونظيره السوري الدكتور نضال الشعار، عُقد في دمشق أول اجتماع فني تفاوضي لمتابعة الملفات التجارية وبدء العمل عليها عبر القنوات الفنية المختصة.
+وضمّ الوفد اللبناني المدير العام لوزارة الاقتصاد والتجارة الدكتور محمد أبو حيدر، ومستشارة وزير الاقتصاد والتجارة الدكتورة ريما يونس، إلى جانب ممثلين عن المجلس الأعلى للجمارك والمديرية العامة للجمارك ورئاسة مجلس الوزراء.
+وتناول الاجتماع الرسوم والبدلات الجمركية وغير الجمركية وتكاليف العبور والنقل، وسبل تكوين صورة شاملة وواضحة حول الأعباء المترتبة على حركة السلع في الاتجاهين. كما تبادل الجانبان وجهات النظر بشأن أسس احتساب الرسوم والبدلات والتخفيضات المطبقة على بعض مسارات النقل، وأثر هذه التكاليف على حركة التبادل التجاري.
+واتفق الجانبان على استكمال تبادل البيانات والمعلومات الفنية ذات الصلة، بما يشمل الرسوم والبدلات والإعفاءات أو التخفيضات وآليات احتسابها، وإعداد أمثلة عملية عن السلع التي تتأثر كلفتها بهذه الرسوم، تمهيداً لمناقشة المسائل المطروحة في الاجتماعات المقبلة. كما بحثا سبل تحسين حركة الشاحنات والبضائع عبر المعابر، وتطوير التنسيق وتبادل المعلومات بين الجهات المختصة.
+وناقش الجانبان الأفكار الأولية لمشروع اتفاق ينظّم التجارة بين البلدين ويعزز الشراكة التجارية ويسهّل حركة السلع. واتفقا على مواصلة العمل الفني بوتيرة مكثفة خلال الأسابيع المقبلة، بهدف تطوير هذه الأفكار واستكمال مناقشتها والتقدم نحو بلورة تفاهمات عملية تخدم المصالح المشتركة.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:08:36.275389+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>الأخبار | أبو حيدر: بدء التنسيق مع الجانب السوري لتعزيز التبادل التجاري وتسهيل الإجراءات الجمركية | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/أبو-حيدر-بدء-التنسيق-مع-الجانب-السوري-لتعزيز-التبادل-التجاري-وتسهيل-الإجراءات-الجمركية</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>الجمهورية اللبنانية 
+أبو حيدر: بدء التنسيق مع الجانب السوري لتعزيز التبادل التجاري وتسهيل الإجراءات الجمركية
+في إطار متابعة مخرجات اللقاء الأخير الذي جمع وزيري الاقتصاد في لبنان وسوريا، بدأ الفريق التقني عبر المدير العام للاقتصاد والتجارة الدكتور محمد أبو حيدر التواصل والتنسيق مع الجانب السوري، بهدف وضع التفاهمات المشتركة موضع التنفيذ، وتعزيز التعاون الاقتصادي والتجاري بين البلدين.
+وفي هذا السياق، عُقد اجتماع في مقر وزارة الاقتصاد والصناعة السورية، بمشاركة ممثلين عن الجهات المعنية بالشؤون الاقتصادية والجمركية والنقل في البلدين، خُصّص لبحث سبل تنشيط التبادل التجاري، وتسهيل حركة انسياب البضائع عبر المعابر الحدودية، ومعالجة العقبات التي تواجه حركة التجارة بين لبنان وسوريا.
+وتناول الاجتماع المقترحات اللبنانية الرامية إلى وضع إطار عملي للمفاوضات وتحديد أولويات العمل للمرحلة المقبلة، إضافة إلى مراجعة الرسوم الجمركية والرسوم وتكاليف الخدمات المفروضة على السلع والبضائع عبر المنافذ الحدودية، ودراسة السبل الكفيلة بتخفيض تكاليف التجارة وتبسيط الإجراءات ذات الصلة.
+وأكدت هذه الخطوة أهمية الانتقال من التفاهمات إلى العمل التنفيذي، من خلال التواصل المباشر والتنسيق المؤسسي بين الجهات المختصة، بما يسهم في إزالة العوائق أمام التجارة، وتحسين بيئة الأعمال، وتعزيز تنافسية المنتجات اللبنانية والسورية في الأسواق.
+ويأتي هذا المسار في إطار الحرص على بناء علاقات اقتصادية وتجارية أكثر فاعلية بين البلدين، بما يخدم المصالح المشتركة، ويفتح آفاقاً أوسع أمام القطاع الخاص والمنتجين والتجار، ويعزز فرص النمو الاقتصادي في لبنان وسوريا.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:08:40.319561+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>الأخبار | البساط استقبل السفير الألماني وبحث معه العلاقات الثنائية وفرص التعاون | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/البساط-استقبل-السفير-الألماني-وبحث-معه-العلاقات-الثنائية-وفرص-التعاون</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>الجمهورية اللبنانية 
+البساط استقبل السفير الألماني وبحث معه العلاقات الثنائية وفرص التعاون
+                            الجمعة 09 تشرين الأول 2026
+*البساط استقبل السفير الألماني وبحث معه العلاقات الثنائية وفرص التعاون*
+استقبل وزير الاقتصاد والتجارة الدكتور عامر البساط، اليوم، السفير الألماني في لبنان توماس تسانايزن، في زيارة خُصّصت للبحث في العلاقات الثنائية بين لبنان وألمانيا، والتطورات الاقتصادية الراهنة، وآفاق تعزيز التعاون الاقتصادي والتجاري بين البلدين.
+وتناول اللقاء الأوضاع الاقتصادية العامة، وأهمية مواصلة التنسيق والتعاون بما يساهم في تطوير العلاقات الاقتصادية والتجارية اللبنانية-الألمانية، وتعزيز الشراكة بين البلدين بما يخدم مصالحهما المشتركة. 
+حول الكاتب: الوزير
+كان لوريم إيبسوم ولايزال المعيار للنص الشكلي منذ القرن الخامس عشر عندما قامت مطبعة مجهولة برص مجموعة من الأحرف بشكل عشوائي أخذتها من نص. لوريم إيبسوم هو ببساطة نص شكلي، بمعنى أن الغاية هي الشكل وليس المحتوى. ويُستخدم في صناعات المطابع ودور النشر. كان لوريم إيبسوم ولايزال المعيار للنص الشكلي منذ القرن الخامس عشر عندما قامت مطبعة مجهولة برص مجموعة من الأحرف بشكل عشوائي أخذتها من نص، لتكوّن كتيّب بمثابة دليل أو مرجع شكلي لهذه الأحرف.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:08:44.607294+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>الأخبار | أبو حيدر من أبوظبي: نعمل على تحويل الحضور اللبناني في المعارض إلى فرص تصديرية وشراكات تجارية | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/أبو-حيدر-من-أبوظبي-نعمل-على-تحويل-الحضور-اللبناني-في-المعارض-إلى-فرص-تصديرية-وشراكات-تجارية</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>الجمهورية اللبنانية 
+أبو حيدر من أبوظبي: نعمل على تحويل الحضور اللبناني في المعارض إلى فرص تصديرية وشراكات تجارية
+شارك المدير العام لوزارة الاقتصاد والتجارة الدكتور محمد أبو حيدر اليوم في افتتاح الجناح اللبناني في معرض أبوظبي الدولي للأغذية، بحضور سفير لبنان لدى دولة الإمارات العربية المتحدة الأستاذ طارق منعمّنة، وممثلين عن جمعية Qoot ومجلس الأعمال الإماراتي اللبناني ممثلاً بالسيد سفيان صالح، إلى جانب عدد من الصناعيين والمزارعين والمصدرين اللبنانيين.
+وأكد أبو حيدر أن المشاركة اللبنانية في المعارض الدولية، ولا سيما في الأسواق العربية، تشكل فرصة أساسية للتعريف بالمنتجات اللبنانية وتعزيز حضورها، مشدداً على أن تسويق المنتج اللبناني وفتح أسواق جديدة أمامه يشكلان جزءاً أساسياً من دعم القطاعات الإنتاجية وتعزيز الصادرات وتحفيز النمو الاقتصادي.
+وأشار إلى أن لبنان يمتلك منتجات ذات جودة عالية وقادرة على المنافسة في الأسواق الخارجية، لافتاً إلى أهمية الانتقال من مجرد المشاركة في المعارض إلى بناء شراكات تجارية مستدامة وربط المنتج اللبناني مباشرة بالمستوردين والموزعين ونقاط البيع والمستهلكين في الأسواق المستهدفة.
+وفي هذا الإطار، اختُتمت المشاركة اللبنانية في أبوظبي بلقاء استضافته السفارة اللبنانية في دولة الإمارات العربية المتحدة، وجمع عدداً من المصدرين اللبنانيين مع ممثلين عن نقاط البيع والمستوردين في السوق الإماراتية، بهدف تسهيل التواصل المباشر بينهم وفتح قنوات جديدة لتسويق وتصريف المنتجات اللبنانية.
+وتوجّه أبو حيدر بالشكر إلى سفير لبنان في دولة الإمارات العربية المتحدة الأستاذ طارق منعمّنة على دعمه وحضوره ومبادرته إلى استضافة هذا اللقاء، معتبراً أن دور السفارة والجالية اللبنانية في دولة الإمارات يشكل عاملاً أساسياً في دعم المنتج اللبناني وتعزيز التواصل بين القطاع الإنتاجي اللبناني والأسواق الإماراتية.
+كما ثمّن أبو حيدر دور الجالية اللبنانية في دولة الإمارات في دعم المنتجات والصناعات اللبنانية، مؤكداً أن اللبنانيين في الخارج يشكلون جسراً مهماً بين لبنان والأسواق العالمية، ويمكنهم المساهمة في فتح المزيد من الفرص أمام المنتج اللبناني وتعزيز حضوره وانتشاره.
+وقال أبو حيدر إن التعاون بين وزارة الاقتصاد والتجارة، والسفارات اللبنانية، والقطاع الخاص، والمجالس الاقتصادية، والجاليات اللبنانية في الخارج يمكن أن يشكل منصة عملية لتحويل المعارض والفعاليات الاقتصادية إلى فرص تجارية حقيقية.
+وأكد أن الهدف هو ألا تقتصر المشاركة اللبنانية على عرض المنتجات، بل أن تتبعها لقاءات مباشرة، واتفاقات تجارية، وطلبات تصدير، وشراكات مستدامة تساهم في زيادة الصادرات اللبنانية وفتح أسواق جديدة أمام الصناعيين والمزارعين والمنتجين.
+وختم أبو حيدر بالتأكيد أن المنتج اللبناني لا يحتاج فقط إلى منصة لعرضه، بل إلى أسواق تُفتح أمامه، وشراكات تُبنى حوله، وفرص حقيقية للوصول إلى المستهلك في الخارج.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:08:48.655333+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>الأخبار | وزير الاقتصاد يستقبل وفداً من من البنك الأوروبي لإعادة الإعمار والتنمية | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/وزير-الاقتصاد-يستقبل-وفداً-من-من-البنك-الأوروبي-لإعادة-الإعمار-والتنمية</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>وزير الاقتصاد يستقبل وفداً من من البنك الأوروبي لإعادة الإعمار والتنمية
+*وزير الاقتصاد يستقبل وفداً من من البنك الأوروبي لإعادة الإعمار والتنمية*
+استقبل وزير الاقتصاد والتجارة د. عامر البساط اليوم، وفداً من البنك الأوروبي لإعادة الإعمار والتنمية، وكان اللقاء مناسبةً للتعرف إلى المدير الإقليمي الجديد لمنطقة شرق المتوسط السيد هاشم عبدالحكيم، يُرافقه مدير السياسة، السيد ديمتري غفيندادزي، ومدير مكتب بيروت أليساندرو فيتاديني.
+وجرى البحث في سبل دعم البنك في لبنان للقطاع العام وتحديث الحوكمة لتعزيز مسار الإصلاح، وكذلك مسألة إقراض القطاع الخاص ودعم الصناعة والطاقة المتجددة والمؤسسات الصغيرة والمتوسطة. 
+حول الكاتب: الوزير
+كان لوريم إيبسوم ولايزال المعيار للنص الشكلي منذ القرن الخامس عشر عندما قامت مطبعة مجهولة برص مجموعة من الأحرف بشكل عشوائي أخذتها من نص. لوريم إيبسوم هو ببساطة نص شكلي، بمعنى أن الغاية هي الشكل وليس المحتوى. ويُستخدم في صناعات المطابع ودور النشر. كان لوريم إيبسوم ولايزال المعيار للنص الشكلي منذ القرن الخامس عشر عندما قامت مطبعة مجهولة برص مجموعة من الأحرف بشكل عشوائي أخذتها من نص، لتكوّن كتيّب بمثابة دليل أو مرجع شكلي لهذه الأحرف.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:08:53.077708+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>الأخبار | البساط من صيدا: ثلاث أولويات لإعادة تنشيط المرفأ وإحياء صيدا القديمة ودعم القطاع الخاص | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/البساط-من-صيدا-ثلاث-أولويات-لإعادة-تنشيط-المرفأ-وإحياء-صيدا-القديمة-ودعم-القطاع-الخاص</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>البساط من صيدا: ثلاث أولويات لإعادة تنشيط المرفأ وإحياء صيدا القديمة ودعم القطاع الخاص
+*البساط من صيدا: ثلاث أولويات لإعادة تنشيط المرفأ وإحياء صيدا القديمة ودعم القطاع الخاص*
+زار وزير الاقتصاد والتجارة الدكتور عامر البساط مدينة صيدا، حيث استهل زيارته بلقاء رئيس البلدية المهندس مصطفى حجازي، بحضور نائب رئيس البلدية الدكتور أحمد عكرة وعدد من أعضاء المجلس البلدي، ومستشارة رئيس البلدية وفاء شعيب، ورئيس مكتب صيدا في جهاز أمن الدولة النقيب أحمد حسين.
+وأشاد البساط بـ”الدور الوطني والتاريخي لمدينة صيدا وصمودها”، مؤكداً أن “لدى الوزارة ثلاث أولويات رئيسية بالتعاون مع البلدية: إعادة تنشيط المرفأ وتعيين مجلس إدارة جديد له في المدى القريب، وإعادة إحياء دور صيدا القديمة كمقصد سياحي وثقافي واجتماعي، ودعم قطاع الأعمال والابتكار والقطاع الخاص في المدينة”.
+وشدد على أهمية صيدا، مؤكداً أن “الحكومة اللبنانية تولي المدينة اهتماماً خاصاً انطلاقاً من أهمية الجنوب وعاصمته وبوابته مدينة صيدا”، مشيراً إلى توجيهات رئيس الحكومة نواف سلام في هذا الإطار.
+وأكد البساط أن الهدف هو وضع الأفكار والرؤى موضع التنفيذ لتطوير صيدا القديمة، “لتصبح رافعة اقتصادية تجارية سياحية تغير هوية صيدا وتعيد ربطها بماضيها التاريخي”، مشدداً على ضرورة رسم الحلول وتحديد آليات تنفيذها، على أن تكون أرضية للقاءات دورية لتقييم ما تم إنجازه.
+وأشاد بالجهود الكبيرة التي تبذلها بلدية صيدا في معالجة الملفات والخدمات اليومية، ومنها ملف تسعيرة المولدات والنفايات والسير والطرقات، مؤكداً: “نحن هنا لنقف معهم ونساعد بأي طريقة ممكنة”.
+وفي إطار زيارته، عقد البساط طاولة مستديرة في “مقهى شرقي” بحضور المهندس سعيد باشو، ونائب رئيس غرفة التجارة في صيدا والجنوب عمر دندشلي، ورئيس البلدية وعدد من ممثلي الهيئات الثقافية والسياحية، حيث بحث المجتمعون سبل تطوير صيدا القديمة وتعزيز دورها السياحي والاقتصادي.
+كما التقى الوزير في غرفة التجارة رواد الأعمال المشاركين في مؤتمر NextGEN، بحضور النائب الدكتور عبد الرحمن البزري، ورئيس بلدية صيدا المهندس مصطفى حجازي، ورئيس غرفة التجارة محمد صالح وعدد من أعضاء مجلس الإدارة، واطلع على مشاريعهم واستمع إلى التحديات التي تواجههم، مؤكداً أهمية دعم قطاع الأعمال والابتكار والقطاع الخاص في المدينة.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:08:57.453494+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>الأخبار | كلمة وزير الاقتصاد ممثلاً رئيس الجمهورية في المنتدى اللبناني السوري للاستثمار | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/كلمة-وزير-الاقتصاد-ممثلاً-رئيس-الجمهورية-في--المنتدى-اللبناني---السوري-للاستثمار</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>كلمة وزير الاقتصاد ممثلاً رئيس الجمهورية في المنتدى اللبناني السوري للاستثمار
+كلمة وزير الاقتصاد ممثلاً رئيس الجمهورية في "المنتدى اللبناني - السوري للاستثمار"
+بيروت - في 23 أيلول 2026
+افتتح رئيس الجمهورية العماد جوزاف عون ممثلاً بوزير الاقتصاد والتجارة الدكتور عامر البساط أعمال المنتدى اللبناني السوري للاستثمار، الذي أقيم برعايته في بيروت.
+وألقى وزير الاقتصاد كلمة راعي المنتدى فخامة رئيس الجمهورية، قائلاً:
+أصدقاؤنا وإخوتنا القادمون من سوريا، أهلا وسهلا بكم في بيروت.
+يُشرّفني أن أُمثّل في هذا المُنتدى السيّد رئيس الجمهورية اللبنانية العماد جوزاف عون، وأن أنقُل إليكم تحياتِ فخامته وتمنّياته لهذا اللقاء بالنجاح، وللعلاقات اللبنانية–السورية بمزيدٍ من الاستقرار والتعاون والازدهار.
+إنّ انعقاد هذا المُنتدى اليوم، يحملُ دلالةً تتجاوز الاقتصاد والاستثمار. فنحن أمام لحظةٍ مختلفةٍ وفرصةٍ لإرساء علاقة جديدة بين بلدينا، أكثر وضوحاً وتوازناً، تقومُ على احترام سيادةِ كلٍّ منهما، وحُسن الجوار، والمصالح المُشتركة.
+ولا يعني بناءُ المستقبل، تجاهل الماضي. فعلاقة لبنان وسوريا حملت الكثير من الروابط، كما حملت تجاربَ تركت آثارها على الشعْبَين. المطلوبُ أن نستخلص دروسها، وأن ننظر إلى الأمام: كيف نُحوّل الجغرافيا التي تجمعنا من واقع مفروضٍ إلى فرصة؟ وكيف نبني علاقةً اقتصاديةً يكونُ فيها نجاح لبنان مصلحةً لسوريا، ونجاحُ سوريا مصلحةً للبنان؟
+هذه هي الرؤية التي عبَّر عنها فخامة الرئيس جوزاف عون، وأكّدها دولةُ الرئيس نواف سلام. ومن دمشق سمعنا أيضاً إرادةً لفتحِ صفحةٍ جديدةٍ مع لبنان، عنوانها الاستقرار والتنمية والتعاون الاقتصادي.
+وخلال لقائنا مع فخامة الرئيس أحمد الشرع، كانت الرسالةُ واضحةً: على الاقتصاد أن يكون جسراً أساسيّاً في بناء هذه العلاقة.
+الصفحة الجديدة تحتاج إلى مضمونٍ. وتحتاج، بصورة خاصة، إلى مؤسساتٍ تعمل، ومصالح واضحة ونتائج يستفيد منها الشعبان. لذلك، أودُّ أن أتوقّف هُنا عند ثلاث أفكار أساسيّة:
+أولاً - الانتقال من النوايا إلى المؤسسات ومن المؤسسات إلى التنفيذ
+خلال الأشهر الماضية، بدأنا خطوات مُهمّة
+- تمّ إنشاءُ اللجنة العُليا اللبنانية–السورية المشتركة برئاسة دولة رئيس مجلس الوزراء عن الجانب اللبناني، ومعالي وزير الخارجية أسعد الشيباني عن الجانب السوري، بما يُوفّر إطاراً أكثر انتظاماً واستدامةً للتعاون بين الدولتين. ونعملُ حالياً على مراجعة ومُناقشة أكثر من أربعين اتفاقاً وبروتوكولاً بين البلدين.
+- أنشأنا آلياتٍ للتنسيق الفني بين الوزارات والإدارات المعنيّة، ونعمَلُ على ملفّاتٍ تُؤثّر مباشرةً في حركة الاقتصاد بين البلدين: المعابر، وحركةُ الشاحنات، والترانزيت، والمُواصفات والفحوصات، والقيود على التجارة، والنقل، وتنقّل رجال وسيدات الأعمال.
+- أطلقنا مجلس الأعمال اللبناني–السوري، للتنسيق المُباشر بين القطاعين الخاصّين للبلدَيْن لأنّنا مُقتنعون أنّ أساس العلاقة اللبنانية السورية لا يأتي إلا من القطاع الخاص.
+في الماضي كانت علاقتنا، في أحيان كثيرة، تتخطّى المؤسّسات. وعلى علاقتنا الجديدة أن تكون أقوى بالمؤسّسات.
+ثانياً - الانتقال من مُعالجة المشاكل إلى صناعة الفرص
+تَسهيلُ حركة التجارة وإزالة العوائق أمران أساسيّان، لكنّ طموحنا يجبُ أن يتجاوزَ زيادة حجم الصادرات والواردات بين البلدين. علينا أن نسأل: ماذا يستطيع اللبنانيون والسوريون أن يُنتجوا معاً؟ وفي أيّ قطاعاتٍ يُمكنهم أن يستثمروا معاً؟ وكيف يُمكنهم الوصول معاً إلى أسواق المنطقة والعالم؟
+هذا السؤال يكتسبُ أهميّةً إضافيةً في ضوءِ التحوّلات التي يَشهدُها الاقتصاد العالميّ. فَـخريطة التجارة في منطقتنا يُعاد رسمها. وهذا يفتح أمام لبنان وسوريا فرصةً استراتيجيّة.
+جائحة كورونا كشفت هشاشة سلاسل الإمداد الطويلة. والحروبُ التجاريّة وارتفاع الرسوم الجمركيّة دفعا الدول والشركات إلى تنويع مصادرها وأسواقها وطُرق تجارتها. الحرب الأخيرة والاضطرابات في الممرّات البحرية الإقليمية زادت كلفة الشّحن والمخاطر، وأعادت الاعتبار إلى الطرق البريّة الداخليّة، وإلى تَعدُّد مسارات النقل.
+فَمرافئُ البلديْن تستطيعُ أن تُشكّل منافذ أساسيّةً تربط البحر المتوسّط بالطرق البريّة الممتدّة إلى داخل المنطقة وتتضاعف قيمة هذه المرافئ عندما ترتبط بشبكةٍ حديثةٍ وفعّالةٍ من الطُرق، وخطوط السّكك الحديد، وخطوط نقل الطاقة.
+من هُنا، تكتسبُ مشاريع النقل والترانزيتِ والبُنية التحتيّة بُعداً يَتجاوز تسهيل التجارة الثُنائيّة. فهي تفتح الممرّاتِ الداخلية، وتربطُ أسواقَ المنطقة بِبعضها البعض، وتَمنحُ لبنان وسوريا دوراً في شبكات التجارة الجديدة قيد التشكّل.
+سوريا تمتلك موقعاً استراتيجياً، وسوقاً واسعةً، وقاعدةً إنتاجيّةً، وتُشكّلُ ممرّاً برّياً أساسياً نحو العراق والخليج وتركيا وأسواق أخرى.
+في المقابل، يمتلك لبنان مرافئه، وقطاعه الخاص، وخبراته المهنية والمالية، وطاقاته البشرية، وعلاقاته الاقتصادية، وشبكة انتشار واسعة في المنطقة والعالم.
+فالجمع بين هذه الميزات يمكن أن يفتح فرصا مهمة في الصناعة والزراعة، والصناعات الغذائية والدوائية، والطاقة والنقل، والخدمات اللوجستية، والسياحة والتكنولوجيا والخدمات المهنية.
+هذه هي النقلة التي نريدها: من التبادل التجاري إلى مشاريع وسلاسل قيمة مشتركة، ومن موقع جغرافي نملكه إلى دور اقتصادي نبنيه معاً.
+ثالثاً - تحديد مسؤولية كلِّ طرف في إنجاح هذه الرؤية
+دور الحكومات هو فتح الطريق أمام النشاط الاقتصادي. فعلينا إزالة العوائق، وتبسيط الإجراءات، وخفض كلفة التجارة، وتوفير إطار قانوني واضح ومستقر، وضمان المنافسة العادلة وحماية حقوق المستثمرين.
+بينما دور القطاع الخاص، يرتكز على اكتشاف الفرص، وبناء الشراكات، وتعبئة التمويل، وخلق فرص العمل.
+ولهذا أقول للقطاع الخاص اللبناني: ادرسوا الفرص القائمة في سوريا بجدية. ابحثوا عن الشركاء والمشاريع القابلة للاستمرار. وأبلغونا بوضوح عن العوائق والضمانات والإجراءات التي تحتاجون إليها.
+وسنعمل مع زملائنا في الحكومة السورية على معالجة هذه القضايا ضمن الأطر الرسمية التي بدأنا بإنشائها.
+وأقول لأصدقائنا السوريين: انظروا إلى لبنان كشريك في الاستثمار والخدمات والخبرات والتكنولوجيا، وكصلة وصل مع رؤوس الأموال وشبكات الأعمال والأسواق الخارجية.
+وإلى المستثمر العربي والدولي نقول: إذا جمعنا موقعي البلدين، ومرافئهما ومعابرهما، ومواردهما البشرية، وقدرات قطاعيهما الخاصين، يمكن أن نخلق مشاريع ذات جدوى اقتصادية وإقليمية مهمة.
+السيداتُ والسادة،
+لبنان يريد سوريا مستقرة وآمنة ومزدهرة، لأن استقرار سوريا وازدهارها مصلحة وطنية لبنانية. ولبنان المستقر والمزدهر هو أيضا مصلحة لسوريا. أمامنا هدف واضح : أن نحول موقع بلدينا إلى منصة للإنتاج والتجارة والاستثمار، وأن نربط مرافئنا بالطرق الداخلية والأسواق الإقليمية.
+جدية هذا المسار ستظهر في النتائج: عوائق تزال، ومشاريع تنطلق، واستثمارات تتدفق، وفرص عمل تتزايد.
+الجغرافيا جمعت بلدينا. ومسؤوليتنا اليوم، أن نجعل هذه الجغرافيا تعمل لصالحنا.
+شكراً لكم، وأهلاً وسهلاً بكم في بيروت.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:09:05.510638+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>الأخبار | البساط يطلق استثمار فندق معرض رشيد كرامي الدولي: خطوة محورية في خطة النهوض بطرابلس والشمال | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/البساط-يطلق-استثمار-فندق-معرض-رشيد-كرامي-الدولي-خطوة-محورية-في-خطة-النهوض-بطرابلس-والشمال</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>البساط يطلق استثمار فندق معرض رشيد كرامي الدولي: خطوة محورية في خطة النهوض بطرابلس والشمال
+*البساط يطلق استثمار فندق معرض رشيد كرامي الدولي: خطوة محورية في خطة النهوض بطرابلس والشمال*
+أكد وزير الاقتصاد والتجارة الدكتور عامر البساط أن إطلاق الاستثمار في فندق معرض رشيد كرامي الدولي يشكل خطوة أساسية ضمن رؤية متكاملة لإعادة تفعيل المعرض وتعزيز دوره كرافعة للتنمية الاقتصادية والسياحية في طرابلس والشمال، مشدداً على أن الفندق لا يُنظر إليه كمشروع تجاري منفصل، بل كجزء محوري من مستقبل المدينة والمنظومة الاقتصادية التي يُفترض أن تتكامل فيها المرافق الحيوية، من المرفأ والمطار والمنطقة الاقتصادية إلى المعرض.
+وجاء كلام البساط خلال مؤتمر صحافي عقده مجلس إدارة معرض رشيد كرامي الدولي برعايته وحضوره، لإطلاق مزايدة استثمار فندق المعرض والإعلان عن تفاصيل المشروع وشروط المشاركة فيه، بحضور عدد من النواب والمسؤولين ورؤساء الهيئات الاقتصادية والنقابية والبلدية وحشد من الفعاليات الاقتصادية في طرابلس والشمال.
+وأشار البساط إلى أن إطلاق الفندق يأتي في إطار خطة أوسع تتضمن إعادة إطلاق مشروع "منجرة"، والعمل على ترميم المعرض وتثبيته وتأهيله ليعود معلماً حضارياً واقتصادياً، لافتاً إلى أن الحركة المتنامية التي يشهدها المعرض تشكل مؤشراً مهماً على دوره المتجدد في تنشيط المدينة. كما كشف عن العمل على تنظيم "ترينالي" دولي كبير في المعرض، بالتعاون مع متخصصين دوليين، بما يعزز قدرته على استضافة فعاليات ومعارض ذات طابع عالمي.
+وأوضح أن خطة إطلاق الفندق استندت إلى دراسات وتحليل مالي ووثيقة شروط وخطة مفهوم عام، مشيداً بجهود مجلس إدارة المعرض في إعداد الملف، ومؤكداً أن المشروع يأتي ضمن خطة تنموية أوسع لطرابلس والشمال.
+من جهته، أعلن رئيس مجلس إدارة المعرض هاني شعراني بدء المرحلة الاستثمارية في مسيرة المعرض، بعد تسجيل نحو 150 حدثاً واستقبال 250 ألف زائر خلال عام، مشيراً إلى أن استثمار الفندق، لمدة 32 عاماً، يتضمن إعادة تأهيله وتشغيله، مع التزام المستثمر بدفع نسبة من المبيعات والتعاقد مع مشغل فندقي عالمي. وأوضح أن سحب دفاتر الشروط يبدأ منتصف تشرين الأول، على أن تُقدّم العروض حتى منتصف كانون الثاني 2027، تمهيداً لفضها خلال الشهر نفسه.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:09:09.804063+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>الأخبار | العمل على تسهيل الإجراءات بين لبنان وسوريا مستمر... البساط: خطوة كبيرة نحو توحيد المواصفات والمقاييس | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/العمل-على-تسهيل-الإجراءات-بين-لبنان-وسوريا-مستمر-البساط-خطوة-كبيرة-نحو-توحيد-المواصفات-والمقاييس</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>الجمهورية اللبنانية 
+العمل على تسهيل الإجراءات بين لبنان وسوريا مستمر... البساط: خطوة كبيرة نحو توحيد المواصفات والمقاييس
+*العمل على تسهيل الإجراءات بين لبنان وسوريا مستمر... البساط: خطوة كبيرة نحو توحيد المواصفات والمقاييس*
+أعلن وزير الاقتصاد والتجارة الدكتور عامر البساط أن العمل على توحيد المواصفات والمقاييس بين لبنان وسوريا قطع شوطاً متقدماً، وبات أقرب إلى التنفيذ خلال الأشهر المقبلة، في إطار مسار أوسع لتسهيل حركة التجارة وانسياب السلع بين البلدين.
+وجاء كلام البساط عقب اجتماع عُقد في وزارة الاقتصاد والتجارة في بيروت مع المدير العام لهيئة المواصفات والمقاييس العربية السورية الدكتور ياسر عليوي، بحضور المدير العام لوزارة الاقتصاد والتجارة الدكتور محمد أبو حيدر، والمديرة العامة لمؤسسة المقاييس والمواصفات اللبنانية (ليبنور) المهندسة لينا درغام. وضمّ الوفد السوري مديرة مكتب التعاون الدولي المهندسة ثراء قبيلي، ومديرة المديرية الكيميائية المهندسة رنيم الشعار، ومدير مديرية ضبط الجودة في الهيئة المهندس فادي عموري.
+وأشار البساط إلى أن العمل يتسارع بهدف الوصول إلى توافق في المواصفات والمقاييس المعتمدة للسلع والبضائع في البلدين، على أن يُستكمل هذا المسار خلال فترة زمنية قصيرة.
+من شأن هذه الخطوة، عملياً، تبسيط الإجراءات اللوجستية والفنية، وفتح المجال أمام الاعتراف المتبادل بنتائج الفحوص والمختبرات المعتمدة في البلدين، بما يخفف الضغط على المعابر الحدودية، ويقلص الوقت الذي تستغرقه عمليات فحص البضائع، ويساهم في تسريع حركة الشاحنات والترانزيت والتبادل التجاري.
+ولا تقتصر هذه الخطوة على توحيد المواصفات والمقاييس، بل تأتي ضمن خطة أوسع لإعادة تنظيم العلاقات الاقتصادية والتجارية بين لبنان وسوريا. وكانت هذه الملفات محوراً أساسياً في مباحثات البساط خلال زيارته إلى دمشق في تموز الماضي، والتي أفضت إلى تشكيل لجنة فنية لمعالجة المشكلات التقنية على المعابر الحدودية، وتسريع عبور البضائع والشاحنات وخفض كلفة الإجراءات، بما يساهم في تسهيل حركة التجارة والنقل بين البلدين.
+يتكامل هذا المسار مع عمل اللجنة العليا اللبنانية-السورية المشتركة، الهادفة إلى وضع إطار أوسع للتعاون الاقتصادي واللوجستي، يشمل قطاعات النقل والكهرباء وأنابيب الغاز والمرافئ.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:09:13.607770+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>الأخبار | البساط يبحث مع الحجار حركة الصادرات ومؤازرة جولات وزارة الاقتصاد الرقابية | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/البساط-يبحث-مع-الحجار-حركة-الصادرات-ومؤازرة-جولات-وزارة-الاقتصاد-الرقابية</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>البساط يبحث مع الحجار حركة الصادرات ومؤازرة جولات وزارة الاقتصاد الرقابية
+*البساط يبحث مع الحجار حركة الصادرات ومؤازرة جولات وزارة الاقتصاد الرقابية*
+بحث وزير الاقتصاد والتجارة عامر البساط، مع وزير الداخلية والبلديات أحمد الحجار، تعزيز التعاون والتنسيق بين الوزارتين بما يخص حركة الصادرات اللبنانية وتعزيز آليات الرقابة.
+كما بحث البساط مع الحجار تشديد التنسيق مع القوى الأمنية والبلديات لمؤازرة الجولات الرقابية الميدانية لوزارة الاقتصاد والتجارة، واستخدام كل الوسائل الرقابية المتاحة لمراقبة أسعار السلع والمولدات وضبط المخالفين ومكافحة التضخم.
+لاسيما وأن وزارة الاقتصاد قد نفّذت منذ بداية العام نحو 16 ألف كشف ميداني، وسطرت نحو 700 محضر ضبط، وأحالت عشرات المولدات المخالفة الى المدعي العام المالي والنائب العام الاستئنافي، كما صادرت عدداً منها بالتعاون مع الأجهزة الأمنية لصالح البلديات. 
+حول الكاتب: الوزير
+كان لوريم إيبسوم ولايزال المعيار للنص الشكلي منذ القرن الخامس عشر عندما قامت مطبعة مجهولة برص مجموعة من الأحرف بشكل عشوائي أخذتها من نص. لوريم إيبسوم هو ببساطة نص شكلي، بمعنى أن الغاية هي الشكل وليس المحتوى. ويُستخدم في صناعات المطابع ودور النشر. كان لوريم إيبسوم ولايزال المعيار للنص الشكلي منذ القرن الخامس عشر عندما قامت مطبعة مجهولة برص مجموعة من الأحرف بشكل عشوائي أخذتها من نص، لتكوّن كتيّب بمثابة دليل أو مرجع شكلي لهذه الأحرف.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:09:17.718176+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>الأخبار | وزير الاقتصاد والتجارة يلتقي وفداً من مؤسسة التمويل الدولية | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/وزير-الاقتصاد-والتجارة-يلتقي-وفداً-من-مؤسسة-التمويل-الدولية</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>وزير الاقتصاد والتجارة يلتقي وفداً من مؤسسة التمويل الدولية
+*وزير الاقتصاد والتجارة يلتقي وفداً من مؤسسة التمويل الدولية*
+التقى وزير الاقتصاد والتجارة عامر البساط وفداً من مؤسسة التمويل الدولية (IFC) ضمّ المدير الإقليمي المغادر، السيد خواجة أفتاب أحمد، والمدير الإقليمي الجديد، السيد توماس جاكوبس، وذلك في إطار متابعة التعاون القائم بين الوزارة والمؤسسة.
+وأعرب الوزير عن تقديره للجهود التي بذلها أحمد خلال فترة تولّيه مهامه، مثمّناً دعمه للتعاون بين الجانبين، كما رحّب بجاكوبس متمنياً له التوفيق في مهامه الجديدة، ومؤكداً الحرص على مواصلة التعاون وتعزيز الشراكة مع المؤسسة دعماً لمسار الإصلاح والتنمية الاقتصادية في لبنان. 
+حول الكاتب: الوزير
+كان لوريم إيبسوم ولايزال المعيار للنص الشكلي منذ القرن الخامس عشر عندما قامت مطبعة مجهولة برص مجموعة من الأحرف بشكل عشوائي أخذتها من نص. لوريم إيبسوم هو ببساطة نص شكلي، بمعنى أن الغاية هي الشكل وليس المحتوى. ويُستخدم في صناعات المطابع ودور النشر. كان لوريم إيبسوم ولايزال المعيار للنص الشكلي منذ القرن الخامس عشر عندما قامت مطبعة مجهولة برص مجموعة من الأحرف بشكل عشوائي أخذتها من نص، لتكوّن كتيّب بمثابة دليل أو مرجع شكلي لهذه الأحرف.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:09:21.942309+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>الأخبار | الإمارات ولبنان توقّعان مذكرة تفاهم لتعزيز التعاون التجاري والاستثماري | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/الإمارات-ولبنان-توقّعان-مذكرة-تفاهم-لتعزيز-التعاون-التجاري-والاستثماري</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>الجمهورية اللبنانية 
+الإمارات ولبنان توقّعان مذكرة تفاهم لتعزيز التعاون التجاري والاستثماري
+*الإمارات ولبنان توقّعان مذكرة تفاهم لتعزيز التعاون التجاري والاستثماري*
+وقّع وزير الاقتصاد والتجارة في الجمهورية اللبنانية الدكتور عامر البساط، ووزير التجارة الخارجية في دولة الإمارات العربية المتحدة الدكتور ثاني بن أحمد الزيودي، مذكرة تفاهم بين الجانبين تهدف إلى تعزيز التعاون في مجالي التبادل التجاري والاستثمار، وتطوير الشراكة الاقتصادية بين البلدين، بما يخدم المصالح المشتركة ويعزّز العلاقات الثنائية.
+وأكد الجانبان أن المذكرة تشكّل خطوة عملية لترجمة العلاقات التاريخية والاقتصادية الراسخة بين لبنان والإمارات إلى مزيد من التعاون الحكومي.
+ووصف وزير التجارة الخارجية الإماراتي الزيارة إلى لبنان بالناجحة، مشيراً إلى أنها أتاحت استكشاف قطاعات وفرص جديدة للتعاون التجاري والاستثماري، تمهيداً لوضع مسارات عمل واضحة بين الجهات الحكومية وفتح آفاق أوسع أمام القطاع الخاص ومجالس الأعمال، ولا سيما العمل على دعم القطاعات الحيوية، من بينها الطاقة والتكنولوجيا والخدمات اللوجستية.
+من جهته، أكد وزير الاقتصاد والتجارة اللبناني أن مذكرة التفاهم تعكس إرادة مشتركة للارتقاء بالعلاقات اللبنانية–الإماراتية نحو شراكة اقتصادية أعمق وأكثر تكاملاً، مشدداً على أن لبنان يمتلك إمكانات وقدرات كبيرة يمكن تحويلها إلى نمو مستدام من خلال الإصلاح، وتعزيز دور القطاع الخاص، وتوسيع الشراكات مع الدول العربية، وفي مقدّمها دولة الإمارات.
+وتندرج المذكرة في إطار مسار تعزيز الشراكة الاقتصادية بين البلدين، على أساس المصالح المشتركة، بما يفتح المجال أمام فرص جديدة تعود بالنفع على الاقتصادين والشعبين.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:09:26.091534+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>الأخبار | أمام وفد إماراتي رفيع المستوى… وزير الاقتصاد عامر البساط: لبنان لم يُشطب من الحسابات وعلينا تحويل العلاقة مع الإمارات إلى شراكة اقتصادية أعمق | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/أمام-وفد-إماراتي-رفيع-المستوى…-وزير-الاقتصاد-عامر-البساط-لبنان-لم-يُشطب-من-الحسابات-وعلينا-تحويل-العلاقة-مع-الإمارات-إلى-شراكة-اقتصادية-أعمق</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>الجمهورية اللبنانية 
+أمام وفد إماراتي رفيع المستوى… وزير الاقتصاد عامر البساط: لبنان لم يُشطب من الحسابات وعلينا تحويل العلاقة مع الإمارات إلى شراكة اقتصادية أعمق
+*أمام وفد إماراتي رفيع المستوى… وزير الاقتصاد عامر البساط: لبنان لم يُشطب من الحسابات وعلينا تحويل العلاقة مع الإمارات إلى شراكة اقتصادية أعمق*
+أكد وزير الاقتصاد والتجارة د. عامر البساط أن زيارة الوفد الاقتصادي الإماراتي إلى بيروت تأتي في لحظة مفصليّة يمر فيها لبنان في واحدة من أصعب المراحل في تاريخه الحديث، مشدّداً على أن حضور الوفد في هذه الظروف يحمل رسالة واضحة إلى اللبنانيين والمستثمرين والقطاع الخاص بأن لبنان لم يُشطب من الحسابات.
+وخلال كلمته في افتتاح الملتقى الاقتصادي اللبناني الإماراتي، الذي حضره دولة رئيس مجلس الوزراء نواف سلام ممثلا بدولة نائب رئيس مجلس الوزراء طارق متري، والوفد الاقتصادي الإماراتي برئاسة وزير التجارة الخارجية الإماراتي الدكتور ثاني بن أحمد الزيودي، إلى جانب عدد من الوزراء ورؤساء الهيئات الاقتصادية وغرف التجارة والصناعة ورئيسي مجلسي الأعمال في البلدين، شكر البساط الهيئات الاقتصادية برئاسة الوزير السابق محمد شقير على تنظيمها الملتقى، ورحّب بالوفد الإماراتي مؤكداً أن الزيارة تعكس عمق العلاقات الاقتصادية والإنسانية الراسخة بين لبنان والإمارات.
+وقال البساط إن لبنان يمر بمرحلة صعبة، إذ إنه في حالة حرب، فيما لا يزال اقتصاده يرزح تحت ثقل سنوات من الأزمات، معتبراً أن التظاهر بغير ذلك لا يخدم لبنان ولا يليق بجدية الزيارة.
+وأضاف أن حضور الوفد الإماراتي في هذه المرحلة يحمل وزناً استثنائياً، قائلاً: "في لحظة يحتاج فيها لبنان إلى ثقة أصدقائه أكثر من أي وقت مضى، اخترتم أن تكونوا هنا. وهذه رسالة واضحة إلى اللبنانيين، وإلى المستثمرين، وإلى قطاعنا الخاص: لبنان لم يُشطب من الحسابات".
+وشدّد البساط على أن لبنان والإمارات لا يبدآن علاقة جديدة، بل يبنيان على تاريخ طويل من الروابط الاقتصادية والإنسانية، مشيراً إلى أربع نقاط أساسية.
+وأوضح أولاً، أن قدرات لبنان الإنتاجية أكبر بكثير مما ينتجه اليوم، لافتاً إلى وجود قطاع خاص ديناميكي وكفاءات بشرية استثنائية وعلاقات عميقة مع المنطقة والعالم، وهي مقومات لم تختفِ بسبب الأزمة.
+وأشار إلى أن هذه الإمكانات يُمكن أن تتحول إلى فرصٍ حقيقية، وأن الفرص الاستثمارية الكبرى تبدأ أحيانا قبل اكتمال التعافي، عندما تبدأ ملامحه بالظهور، مؤكدا أن من هنا تأتي أهمية زيارة الوفد الإماراتي.
+وثانياً، أكّد البساط أن الإمكانات وحدها لا تكفي، وأن تحويلها إلى نمو وازدهار يحتاج إلى إصلاح حقيقي للقطاع المصرفي والإطار المالي والخدمات الأساسية وطريقة عمل الدولة.
+وشدد على ضرورة ترسيخ مبدأ سيادة الدولة وحصرية السلاح وكون قرار الحرب والسلم بيد الدولة وحدها، مؤكداً أنه "لا اقتصاد يزدهر، ولا مستثمر يُخطّط بثقة، إذا لم تكن هذه القرارات بيد الدولة وحدها".
+واعتبر البساط ثالثاً، أن التعافي يجب أن يكون في جوهره، مشروع القطاع الخاص، مشيراً إلى أن الإمارات تُقدم نموذجاً مهماً في هذا المجال، من خلال تهيئة شروط النجاح للقطاع الخاص عبر وضوح القواعد، وسهولة ممارسة الأعمال، والتخطيط بعيد المدى، والانفتاح على الكفاءات ورؤوس الأموال والأسواق العالمية. 
+ولفت إلى أن لبنان يمتلك أساساً قوياً للبناء عليه، موضحاً أن القطاع الخاص اللبناني يعد من أكثر القطاعات ريادة في المنطقة، وأن جزءاً كبيراً منه وجد في الإمارات بيتاً ثانياً له. ولفت إلى أن العلاقة بين البلدين تتجاوز التعاون بين وفدين اقتصاديين، معتبراً أن البلدين أمام مجتمع أعمال تربطه علاقات وشراكات بنيت على مدى عقود.
+رابعاً، شدّد البساط على ضرورة تحويل العلاقة بين لبنان والإمارات إلى شراكة اقتصادية أعمق، مشيراً إلى أن من أهم عناصر التجربة الإماراتية اندماجها في الاقتصاد العالمي، وهو ما ترجم عبر اتفاقيات التجارة التي بلغت رقماً قياسياً والشراكات الاقتصادية الشاملة.
+وقال إن لبنان تأخر كثيراً في هذا المجال، مؤكداً أن الوقت حان لتغيير ذلك، وطرح البدء باستكشاف إطار شراكة اقتصادية خاصة بين لبنان والإمارات، يكون مساراً عملياً لتعميق التجارة والاستثمار ونقل المعرفة وربط الشركات والأسواق في البلدين. وأكد أن لبنان يُريد في هذا المسار ليس فقط شراكة الإمارات، بل أيضاً الاستفادة من تجربتها وخبرتها.
+وفي ختام كلمته، أكد البساط أن رسالة لبنان واضحة، وهي أن البلاد تملك قدرات أكبر بكثير من واقعها الحالي، وأن تحويل هذه القدرات إلى نمو يحتاج إلى إصلاح وسيادة، فيما يجب أن يقود القطاع الخاص عملية التعافي، ويمكن للإمارات أن تكون شريكاً أساسياً فيها.
+وكان الوزير البساط، قد عقد لقاءً ثنائياً مع نظيره الوزير الزيودي، لبحث فرص التعاون والاستثمار، وأُعلن إثر الاجتماع عن توقيع مذكرة تفاهم بين الوزارتين يوم غد الخميس.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:09:30.136908+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>الأخبار | تعاون جديد بين وزارة الاقتصاد وجمعية المستهلك لتلقي شكاوى المواطنين | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/تعاون-جديد-بين-وزارة-الاقتصاد-وجمعية-المستهلك-لتلقي-شكاوى-المواطنين</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>تعاون جديد بين وزارة الاقتصاد وجمعية المستهلك لتلقي شكاوى المواطنين
+*تعاون جديد بين وزارة الاقتصاد وجمعية المستهلك لتلقي شكاوى المواطنين*
+عُقد لقاء في وزارة الاقتصاد والتجارة برئاسة معالي وزير الاقتصاد عامر البساط، وحضور المدير العام للوزارة محمد أبو حيدر، ورئيس جمعية المستهلك زهير برو، ونائبة الرئيس د. ندى نعمي، وذلك في إطار تعزيز التعاون والتنسيق المشترك لمواكبة تطبيق قانون حماية المستهلك الجديد الذي أقرّه مجلس النواب مؤخراً، وتشجيع  المستهلكين على التبليغ عن أي شكوى بهدف تحقيق الاستجابة السريعة.
+وأكد الجانبان أن جمعية المستهلك-لبنان تمثل شريكاً أساسياً في أي نقاش أو مسار يهدف إلى تطوير منظومة حماية المستهلك وتعزيز الرقابة على الأسواق، انطلاقاً من دورها في في رصد المخالفات والتواصل المباشر مع المواطنين.
+واتُّفق خلال اللقاء على تفعيل آلية تعاون مشتركة لتلقي شكاوى المواطنين عبر الخط الساخن الخاص بالجمعية (01750650)، على أن تُحال إلى وزارة الاقتصاد والتجارة لاتخاذ الإجراءات اللازمة، بما يضمن سرعة الاستجابة وفعالية المتابعة، في إطار شراكة مؤسساتية تخدم المصلحة العامة.
+ويأتي هذا التعاون بالتوازي مع استمرار الوزارة في استقبال الشكاوى عبر تطبيقها الإلكتروني (MoET Digital Services)، بما يوسّع قنوات التواصل مع المواطنين ويعزز الاستجابة السريعة والرقابة، في إطار التطبيق الفعّال لأحكام قانون حماية المستهلك الجديد الذي رفعت تعديلاته من الغرامات على المخالفين وهو ما يُحمّلهم مسؤولية وطنية وإنسانية في ظلّ الظروف الصعبة.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:09:34.301961+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>الأخبار | وزير الاقتصاد من صيدا تفعيل دور المرفأ والواجهة البحرية مدخل لرؤية تنموية تعيد للمدينة دورها الاقتصادي | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/وزير-الاقتصاد-من-صيدا-تفعيل-دور-المرفأ-والواجهة-البحرية-مدخل-لرؤية-تنموية-تعيد-للمدينة-دورها-الاقتصادي</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>وزير الاقتصاد من صيدا تفعيل دور المرفأ والواجهة البحرية مدخل لرؤية تنموية تعيد للمدينة دورها الاقتصادي
+*وزير الاقتصاد من صيدا: تفعيل دور المرفأ والواجهة البحرية مدخل لرؤية تنموية تعيد للمدينة دورها الاقتصادي*
+أكد وزير الاقتصاد والتجارة عامر البساط أن مدينة صيدا هي مدينة الانفتاح والتعددية وتمتلك مقومات اقتصادية وتنموية كبيرة تؤهلها للعب دور محوري على مستوى لبنان، مشدداً على أهمية إعادة تفعيل دور مرفئها والواجهة البحرية ضمن رؤية تنموية متكاملة تعزز النمو المتوازن بين المناطق.
+تصريح البساط جاء خلال زيارة قام بها إلى المدينة، استهلها من مرفأ صيدا، يرافقه مستشار رئيس الحكومة للإعمار والتنمية الدكتور ساطع الأرناؤوط، حيث كان في استقباله عدد من المسؤولين والفاعليات الاقتصادية والبلدية، في مقدمهم رئيس بلدية صيدا المهندس مصطفى حجازي، رئيسة مصلحة الاقتصاد في الجنوب ميساء حدرج، رئيس جمعية تجار صيدا وضواحيها علي الشريف، وعدد من المعنيين بالمرفأ والقطاعات الاقتصادية.
+وشملت جولة الوزير زيارة مرفأ صيدا، وغرفة التجارة والصناعة والزراعة في صيدا والجنوب، وميناء الصيادين وسوق السمك، إضافة إلى سوق صيدا التجاري، حيث اطلع على واقع القطاعات الاقتصادية والتحديات التي تواجهها، والتقى عددًا من الفاعليات والتجار.
+وخلال زيارته غرفة التجارة والصناعة والزراعة في صيدا والجنوب، عقد الوزير البساط اجتماعاً موسعاً مع رئيس الغرفة محمد حسن صالح وأعضاء الغرفة، استمع خلاله إلى هواجس القطاعين التجاري والاقتصادي، إضافة إلى أوضاع القطاعات الصناعية والزراعية وسبل دعمها.
+وقال الوزير البساط إن “دور صيدا مهم جداً، سواء من حيث موقعها الجغرافي وتواصلها مع الجنوب وبيروت ومحيطها، أو من خلال إرثها الثقافي ودورها الاقتصادي”، لافتاً إلى أن المدينة “بوابة الجنوب” وتمتلك مقومات أساسية، بينها المرفأ والتعليم والقدرات البشرية، بما يسمح لها بأن تؤدي دوراً أكبر بكثير من الدور الذي تؤديه اليوم.
+وشدد على أن “الإنماء المتوازن بين المناطق هو أمر أساسي”، مؤكداً أن صيدا يجب أن تكون جزءاً أساسياً منه، وأنها تمتلك كل المقومات التي تؤهلها لتكون مدينة محورية اقتصادياً وتنموياً.
+وأشار الوزير إلى أن “بدء الزيارة من المرفأ لم يكن مصادفة”، موضحاً أن هذا المرفق يشكل ركيزة أساسية في أي رؤية مستقبلية للمدينة، وأن المطلوب هو إعادة التفكير بدور صيدا الاقتصادي والاجتماعي والثقافي ضمن خطة تنموية طويلة المدى.
+وأكد البساط أن الحكومة تقف إلى جانب صيدا وتقدّر الدور الذي لعبته خلال الظروف الصعبة، مشدداً على أن المرحلة المقبلة تتطلب العمل على مشاريع تعزز مكانة المدينة، انطلاقاً من الواجهة البحرية والمرفأ، وصولاً إلى مختلف القطاعات الإنتاجية.
+واختتم الوزير جولته بزيارة ميناء الصيادين وسوق السمك، حيث اطلع على أوضاع الصيادين ومطالبهم، قبل أن ينتقل إلى سوق صيدا التجاري لمتابعة واقع الحركة التجارية والتحديات التي يواجهها التجار.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:09:38.638396+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>الأخبار | وزير الاقتصاد من النبطية نقف إلى جانب أهلنا ونعمل لإعادة الحياة إلى الجنوب | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/وزير-الاقتصاد-من-النبطية--نقف-إلى-جانب-أهلنا-ونعمل-لإعادة-الحياة-إلى-الجنوب</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>وزير الاقتصاد من النبطية نقف إلى جانب أهلنا ونعمل لإعادة الحياة إلى الجنوب
+*وزير الاقتصاد من النبطية: نقف إلى جانب أهلنا ونعمل لإعادة الحياة إلى الجنوب*
+أكد وزير الاقتصاد والتجارة عامر البساط أن الوقوف إلى جانب أهالي الجنوب واجب ومسؤولية، مشدداً على التزام الحكومة بإعادة تأهيل البنى التحتية وتأمين مقومات الحياة الأساسية وعودة مؤسسات الدولة تمهيداً لعودة السكان والاستقرار وإعادة الإعمار.
+تصريح البساط جاء خلال جولة تفقدية في مدينة النبطية، برفقة المدير العام للوزارة محمد أبو حيدر، للاطلاع على حجم الأضرار والدمار الذي خلّفته الحرب، ومتابعة مسار عودة مؤسسات الدولة والمواطنين إلى المدينة وبلدات المنطقة وقراها.
+وشارك في الجولة النائبان ناصر جابر وهاني قبيسي، ورئيس بلدية النبطية عباس فخر الدين، حيث عقد البساط سلسلة لقاءات في مركز اتحاد بلديات الشقيف – النبطية، بحضور فاعليات المنطقة ورؤساء البلديات وممثلي جمعية التجار، جرى خلالها بحث تداعيات الحرب وسبل دعم الأهالي والمؤسسات التجارية، مع التشديد على ضرورة الإسراع في معالجة الأضرار وتأمين التعويضات اللازمة تمهيداً لإعادة الإعمار.
+وفي إطار جولته، زار الوزير مفتي وإمام مدينة النبطية الشيخ عبد الحسين صادق، حيث تم التداول في أوضاع المنطقة واحتياجاتها في المرحلة المقبلة.
+كما شملت الزيارة السوق التجاري في المدينة الذي تعرض لأضرار كبيرة، إضافة إلى جمعية تجار النبطية، حيث اطلع الوزير على أوضاع التجار والتحديات التي تواجههم في مرحلة ما بعد الحرب.
+وأكد البساط خلال الزيارة أن “الوقوف إلى جانب أهالي الجنوب واجب ومسؤولية”، وقال: “أقف معكم اليوم كإنسان قبل أي موقع رسمي، فما حصل خلال الحربين، وما تكرر منذ عام 2024، أدى إلى مآسٍ إنسانية واجتماعية واقتصادية وخلّف دماراً هائلاً”.
+وأضاف: “زيارتنا اليوم تهدف إلى الاطلاع على حجم الدمار الممنهج الذي أصاب النبطية والجنوب، والواقع الصعب الذي تعيشه المدينة والمنطقة، لكن اهتمامنا لا يقتصر على الحاضر فقط، بل ينصب أيضاً على المستقبل، وعلى دور الحكومة في الوقوف إلى جانب شعبها”.
+وأشار وزير الاقتصاد إلى أن "الحكومة ملتزمة بالجنوب وأهله وأرضه، وأنا ابن الجنوب. أولويتنا في هذه المرحلة هي تأمين مقومات الحياة الأساسية من خلال تأمين الطرقات والكهرباء والمياه والاتصالات إلى سائر البنى التحتية، وهو مسار بدأ تدريجياً بهدف تمكين السكان والتجار من العودة إلى مناطقهم واستعادة دورة الحياة الطبيعية".
+وتابع: "طموحنا في المرحلة المقبلة، هو إعادة الاستقرار والإعمار وعودة النازحين وتأهيل البنى التحتية بما يليق بالسكان، وهذا يتطلب موارد كبيرة نعمل على تأمينها بالتعاون مع شركائنا الدوليين وأشقائنا".
+وشدد على أهمية إعادة تفعيل الإدارات العامة، لافتاً إلى أن “عودة الحياة إلى الجنوب تتطلب عودة مؤسسات الدولة، ومنها عودة مصلحة الاقتصاد إلى العمل بدوام كامل اعتباراً من يوم الاثنين المقبل”.
+وختم البساط بالتأكيد أن “الهدف هو إعادة الاستقرار الأمني، والمضي في مسار الإعمار، ودعم صمود السكان من خلال برامج حكومية متعددة، بعد استكمال مسح الأضرار وتحديد الاحتياجات”.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:09:42.831077+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>الأخبار | الوزير البساط يلتقي الرئيس الشرع وتأكيد على تعزيز التعاون الاقتصادي بما يخدم مصالح الشعبين | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/الوزير-البساط-يلتقي-الرئيس-الشرع-وتأكيد-على-تعزيز-التعاون-الاقتصادي-بما-يخدم-مصالح-الشعبين</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>الوزير البساط يلتقي الرئيس الشرع وتأكيد على تعزيز التعاون الاقتصادي بما يخدم مصالح الشعبين
+*الوزير البساط يلتقي الرئيس الشرع وتأكيد على تعزيز التعاون الاقتصادي بما يخدم مصالح الشعبين*
+زار وزير الاقتصاد والتجارة عامر البساط، فخامة الرئيس السوري أحمد الشرع في قصر الشعب في دمشق، يرافقه وفد لبناني بحضور وزير الاقتصاد والصناعة السوري نضال الشعار.
+وجرى خلال اللقا التأكيد على أهمية تعميق التقارب السوري–اللبناني، انطلاقاً من خصوصية العلاقة بين البلدين، وتفعيله عبر اللجنة الوزارية العليا ومجلس الأعمال اللبناني-السوري. كما شمل النقاش اعتماد مقاربة جديدة للتكامل الاقتصادي والسياسي تضع جودة حياة المواطنين ورفاههم في البلدين كأولوية.
+وتم البحث في تعزيز مشاريع الربط بين البلدين، بما يشمل خطوط نقل النفط والأنابيب والطاقة، وشبكات النقل البرية والبحرية. كما تطوير التعاون في القطاعات الحيوية، لاسيما الخدمات، والسياحة، والقطاع المصرفي، مع تهيئة الظروف لدور أكبر للبنوك في المرحلة المقبلة.
+كما ثمّن اللقاء أهمية الاستفادة من المعرفة المتبادلة بين الشعبين لتعزيز التكامل السوري–اللبناني وبناء ثقة أكبر لدى المستثمرين، مع ضرورة المباشرة بالحلول العملية للملفات العالقة والتقنية بما يخدم المصالح المشتركة. 
+حول الكاتب: الوزير
+كان لوريم إيبسوم ولايزال المعيار للنص الشكلي منذ القرن الخامس عشر عندما قامت مطبعة مجهولة برص مجموعة من الأحرف بشكل عشوائي أخذتها من نص. لوريم إيبسوم هو ببساطة نص شكلي، بمعنى أن الغاية هي الشكل وليس المحتوى. ويُستخدم في صناعات المطابع ودور النشر. كان لوريم إيبسوم ولايزال المعيار للنص الشكلي منذ القرن الخامس عشر عندما قامت مطبعة مجهولة برص مجموعة من الأحرف بشكل عشوائي أخذتها من نص، لتكوّن كتيّب بمثابة دليل أو مرجع شكلي لهذه الأحرف.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:09:51.284929+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>الأخبار | البساط يترأس اجتماعاً لتسهيل التصدير إلى السعودية | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/البساط-يترأس-اجتماعاً--لتسهيل-التصدير-إلى-السعودية</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>البساط يترأس اجتماعاً لتسهيل التصدير إلى السعودية
+البساط يترأس اجتماعاً لتسهيل التصدير إلى السعودية
+*البساط يترأس اجتماعاً  لتسهيل التصدير إلى السعودية*
+ترأس وزير الاقتصاد والتجارة عامر البساط اجتماعاً ضمّ الملحق التجاري في سفارة المملكة العربية السعودية في بيروت، إلى جانب ممثلين عن الوزارات المعنية، وإدارة الجمارك، ومرفأ بيروت، جرى خلاله بحث سبل تسهيل حركة التصدير من لبنان إلى المملكة العربية السعودية، ولا سيما ما يتعلق بإجراءات التسجيل، بما يساهم في تعزيز انسياب الصادرات اللبنانية إلى السوق السعودية.
+كما استقبل البساط وفداً من هيئة فعاليات المجتمع المدني في بيروت، حيث تناول اللقاء عدداً من المشاريع ذات الاهتمام العام، إضافة إلى مناقشة مبادرات تنموية من شأنها تعزيز التعاون وخدمة العاصمة بيروت.
+وفي لقاءٍ آخر مع مجلس الأعمال اللبناني–الألماني، شدّد البساط على أهمية تطوير العلاقات بين لبنان وألمانيا، وتعزيز التعاون الاقتصادي والاستثماري، وتوسيع الشراكات بين القطاعين العام والخاص، بما يساهم في دعم النمو الاقتصادي وتحفيز فرص الاستثمار. 
+حول الكاتب: الوزير
+كان لوريم إيبسوم ولايزال المعيار للنص الشكلي منذ القرن الخامس عشر عندما قامت مطبعة مجهولة برص مجموعة من الأحرف بشكل عشوائي أخذتها من نص. لوريم إيبسوم هو ببساطة نص شكلي، بمعنى أن الغاية هي الشكل وليس المحتوى. ويُستخدم في صناعات المطابع ودور النشر. كان لوريم إيبسوم ولايزال المعيار للنص الشكلي منذ القرن الخامس عشر عندما قامت مطبعة مجهولة برص مجموعة من الأحرف بشكل عشوائي أخذتها من نص، لتكوّن كتيّب بمثابة دليل أو مرجع شكلي لهذه الأحرف.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:09:55.433073+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>الأخبار | وزير الاقتصاد: تراجع أسعار الطاقة وانخفاض الكلفة عالمياً يجب أن ينعكسا على السلع وجيب المستهلك | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/وزير-الاقتصاد-تراجع-أسعار-الطاقة-وانخفاض-الكلفة-عالمياً-يجب-أن-ينعكسا-على-السلع-وجيب-المستهلك</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>الجمهورية اللبنانية 
+وزير الاقتصاد: تراجع أسعار الطاقة وانخفاض الكلفة عالمياً يجب أن ينعكسا على السلع وجيب المستهلك
+وزير الاقتصاد: تراجع أسعار الطاقة وانخفاض الكلفة عالمياً يجب أن ينعكسا على السلع وجيب المستهلك
+عقد وزير الاقتصاد والتجارة د. عامر البساط، اليوم، اجتماعاً مع المستوردين وأصحاب السوبرماركت والتجار لمتابعة الانخفاض المنتظر في أسعار السوق في ظلّ انخفاض أسعار النفط عالمياً.
+وأكد البساط بعد الاجتماع، "أن ارتفاع الأسعار الذي شهدناه في آذار ونيسان الماضيين، بسبب زيادة كلفة الإنتاج والنقل والتأمين وسط الأوضاع الإقليمية، يجب أن يقابله اليوم انخفاض مماثل إثر تراجع الكلفة عالمياً".
+وشدّد على أن "تراجع الأسعار عالمياً، وخصوصاً أسعار المحروقات، يجب أن ينعكس على أسعار السلع في الأسواق المحلية، بشكل سريع وواضح، وهو ما اجتمعنا لبحثه اليوم، ووزارة الاقتصاد تعمل على تكثيف جولاتها الرقابية لحماية المستهلك الذي يمرّ بظروف صعبة للغاية".
+ولفت البساط إلى أن هوامش الأرباح غير المنطقية وغير المبرّرة لن تكون على حساب المواطنين، لافتاً إلى أن "بعض الانخفاضات بدأت تظهر تدريجياً في عدد من السلع منها الخضار واللحوم وبعض المعلبات، لكن ذلك ليس كافياً". وأضاف: "نقوم برصد أسعار نحو 60 سلعة أساسية يومياً، ومع انخفاض سعري البنزين والمازوت، بدأت تظهر بعض الانخفاضات لكن المطلوب أكثر من ذلك”.
+وتابع وزير الاقتصاد: "إنها مؤشرات إيجابية، لكنها لا تزال دون المستوى المطلوب، ونحن نتطلع إلى انخفاض أكبر وأسرع في الأسعار، وسنواصل الضغط على مختلف القطاعات لضمان ترجمة تراجع الكلفة إلى انخفاض فعلي في أسعار البيع للمستهلك”.
+وفي ما يخص تشديد الرقابة على الأسواق، أكد الوزير البساط أن الوزارة ستعتمد الأدوات الرقابية نفسها التي استخدمتها خلال موجة التضخم، لافتاً إلى أن “أكثر من 70 مراقباً ينفذون نحو 100 كشف ميداني أسبوعياً في مختلف المناطق، بالتنسيق مع القضاء والأجهزة الأمنية المعنية، لملاحقة أي مخالفات أو زيادات غير مبررة في الأسعار”.
+كما حثّ البساط على إقرار مشروع قانون حماية المستهلك الجديد في مجلس النواب، والمراسيم التطبيقبة لقانون المنافسة، باعتبارهما من أبرز أدوات تعزيز الرقابة وحماية الأسواق.
+ولدى سؤاله عن قرار مجلس الوزراء تعليق العمل بالمرسوم المتعلق بالرسوم البيئية، أوضح الوزير أن “الفكرة الأساسية للمرسوم لا تزال قائمة، وهي تقوم على مبدأ أن الملوّث يدفع، والمعتمد في العديد من دول العالم لتحميل كلفة معالجة النفايات للجهات المسببة لها، لاسيما وأن هذه الكلفة تعود وتقع على عاتق البلديات والدولة نفسها والبيئة".
+وأوضح وزير الاقتصاد أن “المشكلة لم تكن في المبدأ، بل في توقيت تطبيقه، في ظل الظروف الاقتصادية الصعبة التي يمر بها لبنان، إلى جانب الضغوط التضخمية الأخيرة، وهو ما دفع الحكومة إلى اتخاذ قرار استثنائي بتعليق العمل بالمرسوم”.
+وشدد الوزير البساط على أن وزارة الاقتصاد “ستكون بالمرصاد لأي محاولة لاستغلال الرسوم التي أُعلنت سابقاً لتبرير استمرار رفع الأسعار”، مؤكداً أن “أي زيادات حصلت خلال الأيام الماضية يجب ألا تتحول إلى زيادات دائمة بعد تعليق المرسوم”.
+وأكد البساط أن حماية القدرة الشرائية للمواطنين في تأتي في أولويات الحكومة، والأهم هو الاستفادة من “انخفاض أسعار الطاقة عالمياً لتراجع أسعار السلع في لبنان، وهو ما ستعمل وزارة الاقتصاد على ضمانه من خلال الرقابة والمتابعة الميدانية في الأسابيع المقبلة”.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:10:17.583165+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>الأخبار | إطلاق الدليل القانوني لرائدة ورائد الأعمال بمناسبة يوم المؤسسات المتناهية الصغر والصغيرة والمتوسطة | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/إطلاق-الدليل-القانوني-لرائدة-ورائد-الأعمال--بمناسبة-يوم-المؤسسات-المتناهية-الصغر-والصغيرة-والمتوسطة</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>إطلاق الدليل القانوني لرائدة ورائد الأعمال بمناسبة يوم المؤسسات المتناهية الصغر والصغيرة والمتوسطة
+إطلاق "الدليل القانوني لرائدة ورائد الأعمال" بمناسبة يوم المؤسسات المتناهية الصغر والصغيرة والمتوسطة
+بمناسبة اليوم العالمي للمؤسسات المتناهية الصغر والصغيرة والمتوسطة (MSMEs) الذي يصادف في 27 حزيران، أطلقت الهيئة الوطنية لشؤون المرأة اللبنانية بالتعاون مع وزارة الاقتصاد والتجارة: "الدليل القانوني لرائدة ورائد الأعمال في لبنان"، الذي أُعدّ من قبل شركة صادر ومشاركوه – محامون ومستشارون قانونيون.
+ويأتي هذا الدليل في إطار "برنامج تمكين المرأة في المشرق" Mashreq Gender Facility (MGF) المدعوم من البنك الدولي بتمويل من الحكومة الكنديّة والحكومة النرويجيّة، الذي يهدف الى تعزيز التمكين الاقتصادي للنساء وضمان بيئة داعمة لهنّ.
+يُشكّل هذا الدليل مرجعًا عمليًا لدعم النساء والرجال الراغبات/ين في تأسيس أعمال خاصّة بهن/م، وإدارتها، وتطويرها، من خلال تزويدهن/م بالمرتكزات القانونية الاساسية والارشادات العملية اللازمة لبناء مشروع مستدام وقابل للنمو.
+ويتطرّق هذا الدليل الذي تمّ تطويره باللغتين العربية والانكليزية، والذي يتوفّر على الموقعين الالكترونيين التابعين للهيئة الوطنية لشؤون المرأة اللبنانية ووزارة الاقتصاد والتجارة، الى مختلف المراحل القانونية المرتبطة بريادة الأعمال، بدءًا من اختيار الكيان القانوني المناسب، واجراءات التسجيل، وصولًا الى حماية الملكية الفكرية والعلامات التجارية، بهدف تعزيز الالتزام بالمتطلّبات القانونية وتمكين رائدات ورواد الأعمال من اتخاذ قرارت تجارية وقانونية مدروسة.
+للاطلاع على الدليل القانوني لرائدة ورائد الأعمال، الرجاء الضغط على الرابط التالي:</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:10:21.754250+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>الأخبار | وزير الاقتصاد يستقبل السفير السعودي ويبحث تعزيز التعاون الاقتصادي وتشكيل خلية متابعة لتسهيل الصادرات اللبنانية | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/وزير-الاقتصاد-يستقبل-السفير-السعودي-ويبحث-تعزيز-التعاون-الاقتصادي-وتشكيل-خلية-متابعة-لتسهيل-الصادرات-اللبنانية</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>وزير الاقتصاد يستقبل السفير السعودي ويبحث تعزيز التعاون الاقتصادي وتشكيل خلية متابعة لتسهيل الصادرات اللبنانية
+*وزير الاقتصاد يستقبل السفير السعودي ويبحث تعزيز التعاون الاقتصادي وتشكيل خلية متابعة لتسهيل الصادرات اللبنانية*
+استقبل وزير الاقتصاد والتجارة، عامر البساط اليوم، سعادة سفير المملكة العربية السعودية لدى لبنان، فهد بن عبد الرحمن الدوسري، في زيارة تعارف، جرى خلالها البحث في العلاقات الاقتصادية وسبل تعزيز التعاون بين البلدين.
+وخلال اللقاء، شكر الوزير المملكة العربية السعودية على وقوفها إلى جانب الشعب اللبناني، ولا سيما من خلال قرار رفع الحظر عن الصادرات اللبنانية، لما يشكّله من خطوة داعمة للاقتصاد الوطني وللقطاعات الإنتاجية اللبنانية.
+كما تناول البحث الشؤون الاقتصادية والإجراءات المرتبطة بحركة التصدير بعد رفع الحظر، حيث تم الاتفاق على تشكيل خلية متابعة مشتركة لمعالجة أي عقبات قد تواجه المصدّرين اللبنانيين، بما يضمن سرعة الاستجابة وتسهيل انسياب الصادرات إلى الأسواق السعودية.
+كذلك جرى استعراض الاتفاقيات التي تعمل الحكومتان اللبنانية والسعودية على تفعيلها وتطويرها، بما يخدم المصالح المشتركة ويعزز التعاون الاقتصادي والتجاري بين البلدين.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:10:25.996649+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>الأخبار | البساط في بكركي… بحث بتداعيات الحرب والأوضاع الاقتصادية والجهود الحكومية | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/البساط-في-بكركي…-بحث-بتداعيات-الحرب-والأوضاع-الاقتصادية-والجهود-الحكومية</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>البساط في بكركي… بحث بتداعيات الحرب والأوضاع الاقتصادية والجهود الحكومية
+البساط في بكركي… بحث بتداعيات الحرب والأوضاع  الاقتصادية والجهود الحكومية*
+زار وزير الاقتصاد والتجارة الدكتور عامر البساط صاحب الغبطة والنيافة الكاردينال مار بشارة بطرس الراعي في الصرح البطريركي في بكركي، حيث جرى البحث في الأوضاع الاقتصادية والاجتماعية والمعيشية في لبنان وانعكاسات الحرب على مختلف القطاعات الحيوية.
+وتناول اللقاء التحديات الراهنة التي تواجه اللبنانيين، والجهود المبذولة على المستويين الرسمي والحكومي لتعزيز الاستقرار الاقتصادي وتخفيف الأعباء المعيشية، إضافة إلى سبل دعم الصمود الوطني وتهيئة الظروف الملائمة لاستعادة النمو.
+كما وضع الوزير البساط، البطريرك الراعي في أجواء الواقع الاقتصادي، مؤكداً أهمية ما يملكه لبنان من طاقات وكفاءات بشرية تشكل ركيزة أساسية للنهوض وإعادة بناء الاقتصاد وتعزيز الثقة بالمستقبل.
+حول الكاتب: الوزير
+كان لوريم إيبسوم ولايزال المعيار للنص الشكلي منذ القرن الخامس عشر عندما قامت مطبعة مجهولة برص مجموعة من الأحرف بشكل عشوائي أخذتها من نص. لوريم إيبسوم هو ببساطة نص شكلي، بمعنى أن الغاية هي الشكل وليس المحتوى. ويُستخدم في صناعات المطابع ودور النشر. كان لوريم إيبسوم ولايزال المعيار للنص الشكلي منذ القرن الخامس عشر عندما قامت مطبعة مجهولة برص مجموعة من الأحرف بشكل عشوائي أخذتها من نص، لتكوّن كتيّب بمثابة دليل أو مرجع شكلي لهذه الأحرف.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:10:46.886315+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>الأخبار | مثّل المدير العام لوزارة الاقتصاد والتجارة الدكتور محمد أبو حيدر معالي وزير الاقتصاد والتجارة في الاجتماع الذي عُقد مع الهيئات الاقتصادية والأمين العام لغرفة التجارة الدولية | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/مثّل-المدير-العام-لوزارة-الاقتصاد-والتجارة-الدكتور-محمد-أبو-حيدر-معالي-وزير-الاقتصاد-والتجارة-في-الاجتماع-الذي-عُقد-مع-الهيئات-الاقتصادية-والأمين-العام-لغرفة-التجارة-الدولية</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>مثّل المدير العام لوزارة الاقتصاد والتجارة الدكتور محمد أبو حيدر معالي وزير الاقتصاد والتجارة في الاجتماع الذي عُقد مع الهيئات الاقتصادية والأمين العام لغرفة التجارة الدولية
+مثّل المدير العام لوزارة الاقتصاد والتجارة الدكتور محمد أبو حيدر معالي وزير الاقتصاد والتجارة في الاجتماع الذي عُقد مع الهيئات الاقتصادية والأمين العام لغرفة التجارة الدولية، حيث تم البحث في سبل دعم التعافي الاقتصادي وتعزيز الثقة بلبنان على المستويين المحلي والدولي.
+وأكد أبو حيدر خلال مداخلته أن إعادة الثقة تشكّل المدخل الأساسي للنهوض الاقتصادي، مشدداً على أن ذلك يتطلب المضي في إقرار وتنفيذ القوانين الإصلاحية، ولا سيّما الإصلاحات المرتبطة بالقطاع المصرفي بما يساهم في تعزيز الاستقرار المالي واستعادة الدينامية الاقتصادية.
+كما شدّد على أهمية تسريع مسار الأتمتة والتحول الرقمي في وزارة الاقتصاد والتجارة بهدف تبسيط الإجراءات، تعزيز الشفافية، والحد من البيروقراطية، بما ينعكس إيجاباً على الخدمات المقدّمة للمواطنين والقطاع الخاص.
+وأشار إلى أن تحفيز بيئة الأعمال وتسهيل الإجراءات يبقى من الأولويات الأساسية لدعم القطاع الخاص وتمكينه من أداء دوره كمحرّك رئيسي للنمو الاقتصادي وخلق فرص العمل.
+وأكد أبو حيدر التزام وزارة الاقتصاد والتجارة بالعمل مع مختلف الشركاء لتعزيز مقومات التعافي الاقتصادي المستدام وترسيخ مناخ من الثقة والإصلاح</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:11:17.275655+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>الأخبار | وزارة الاقتصاد تنظم اجتماعاً تنسيقياً رفيع المستوى لتسريع دعم المؤسسات الصغيرة والمتوسطة في لبنان | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/وزارة-الاقتصاد-تنظم-اجتماعاً-تنسيقياً-رفيع-المستوى-لتسريع-دعم-المؤسسات-الصغيرة-والمتوسطة-في-لبنان</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>الجمهورية اللبنانية 
+وزارة الاقتصاد تنظم اجتماعاً تنسيقياً رفيع المستوى لتسريع دعم المؤسسات الصغيرة والمتوسطة في لبنان
+*وزارة الاقتصاد تنظم اجتماعاً تنسيقياً رفيع المستوى لتسريع دعم المؤسسات الصغيرة والمتوسطة في لبنان… البساط: "القطاع يُشكّل 95% من إجمالي المؤسسات المسجلة والوعود بدعم بعشرات ملايين الدولارات"*
+عقدت وزارة الاقتصاد والتجارة، اليوم الاثنين، اجتماعاً تنسيقياً رفيع المستوى لبحث آليات الدعم العاجل للمؤسسات الصغيرة والمتوسطة ومتناهية الصغر (MSMEs)، بمشاركة سفراء وممثلين عن الجهات الدولية المانحة والمؤسسات المالية ومؤسسات التمويل الأصغر والشركاء التنمويين، في ظل التحديات الاقتصادية والضغوط المتراكمة التي يواجهها لبنان.
+وأكد وزير الاقتصاد والتجارة، د. عامر البساط، أن لبنان يمرّ بـ"أزمة وجدانية واقتصادية متراكمة منذ سبع سنوات، تفاقمت بفعل الحرب الحالية"، مشيراً إلى أن الوزارة بادرت إلى جمع الجهات المانحة الدولية، وفي مقدّمها الاتحاد الأوروبي والبنك الدولي، إلى جانب المؤسسات العامة والخاصة اللبنانية، بهدف تنسيق الجهود وتسريع دعم المؤسسات الإنتاجية.
+وأوضح البساط أن المؤسسات الصغيرة والمتوسطة ومتناهية الصغر تشكّل العمود الفقري للاقتصاد اللبناني، إذ كانت تمثّل قبل الأزمة نحو 95 في المئة من إجمالي المؤسسات المسجّلة، وتساهم بما يقارب 40 في المئة من الناتج المحلي الإجمالي، إضافة إلى توفير أكثر من نصف فرص العمل في القطاع النظامي.
+وقال: "نجتمع اليوم للتركيز على الشريحة الأكثر عرضة للتأثر، لكنها في الوقت نفسه الأكثر أهمية بالنسبة للتوظيف ودخل الأسر ومسار التعافي الاقتصادي"، لافتاً إلى أن "السيولة تبقى التحدي الأساسي للعديد من المؤسسات"، ما يستدعي توفير منح تشغيلية وآليات تمويل مرنة تساعدها على الاستمرار.
+وأشار إلى أن الوزارة أجرت مسحاً شمل 200 شركة، وتعمل حالياً بالتعاون مع الأمم المتحدة على إطلاق مسح أوسع لتحديد الاحتياجات الفعلية للمؤسسات المتضررة.
+كما كُشف خلال الاجتماع عن وجود استعداد كبير لدى الجهات المانحة لدعم المؤسسات الصغيرة والمتوسطة ومتناهية الصغر وزيادة حجم التمويل المتاح لها، حيث التزم عدد من المانحين بإعادة توجيه جزء من الأموال المرصودة سابقاً نحو الاحتياجات الأكثر إلحاحاً لهذه المؤسسات.
+كذلك، أكد المشاركون وجود عدد كبير من الجهات والمؤسسات الجاهزة والقادرة على استيعاب أموال المانحين وصرفها بسرعة وفعالية.
+وتناول الاجتماع أيضاً إمكانية إطلاق جهود مشتركة بين وزارة الاقتصاد والتجارة ووزارة الشؤون الاجتماعية، بما يسمح باستخدام آلية "أمان" لتوجيه مشاريع "النقد مقابل العمل" (Cash for Work) بصورة أكثر فعالية واستهدافاً.
+كما أشار الوزير إلى أن قيمة الدعم المتاح تُقدّر بحوالي 130 مليون دولار، تشمل منحاً وقروضاً مدعومة من البنك الدولي ودول مانحة، بينها النرويج وكندا، مؤكداً أهمية تسريع وصول هذه البرامج إلى المستفيدين.
+وفي ختام الاجتماع، شدّد البساط على أهمية الحوكمة الرشيدة والشفافية الكاملة في إدارة وصرف هذه الأموال، بما يضمن حسن استخدامها وتحقيق الأثر المطلوب، مؤكداً أن "لبنان لا يستطيع تحمّل خسارة مؤسسات قابلة للاستمرار بسبب بطء الدعم أو تشتته أو صعوبة الوصول إليه".</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:11:21.151827+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>الأخبار | وزير الاقتصاد في جولة تفقدية لسوق الخضار المركزي في بيروت | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/وزير-الاقتصاد-في-جولة-تفقدية-لسوق-الخضار-المركزي-في-بيروت</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>الجمهورية اللبنانية 
+وزير الاقتصاد في جولة تفقدية لسوق الخضار المركزي في بيروت
+*وزير الاقتصاد في جولة تفقدية لسوق الخضار المركزي في بيروت*
+جال وزير الاقتصاد والتجارة، د. عامر البساط، ووزير الزراعة نزار هاني، على السوق المركزي للخضار والفاكهة (بالمفرق) في بيروت، في منطقة أرض جلول – قصقص، يُرافقهما المديران العامان لوزارتي الاقتصاد محمد أبو حيدر، والزراعة لويس لحود، ووفد ضمّ رئيس بلدية بيروت إبراهيم زيدان، وعدداً من أعضاء المجلس البلدي، ورئيس نقابة تجار الخضار والفواكه بالمفرق سهيل المعبي، ومعنيين.
+واطّلع الوفد خلال الجولة على واقع السوق واحتياجاته اللوجستية والتنظيمية، واستمع إلى مطالب التجار والهواجس المرتبطة بإعادة تشغيله.
+وشدّد البساط على أهمية تشغيل هذا المرفق الحيوي، نظراً لما له من دور أساسي في تنظيم حركة بيع الخضار والفاكهة في العاصمة، وتخفيف الأعباء عن الأسواق العشوائية، فضلاً عن أهميته كمركز للتلاقي، ولتشغيل اليد العاملة، وضرورة عدم تركه من دون استعمال أو إهمال.
+وأكد أن إعادة تفعيل السوق ستساهم في تنشيط الحركة الاقتصادية في بيروت، وتحسين سلاسل التوريد، وتعزيز الأمن الغذائي، إضافة إلى تعزيز الرقابة وضمان جودة المنتجات ضمن مكان واحد خاضع للرقابة والتنظيم وإجراء الفحوصات المخبرية اللازمة.
+كما أعلن عن تشكيل لجنة مصغّرة لمتابعة ملف تأهيل السوق المركزي، والعمل على إعادة فتحه في أقرب وقت ممكن، وحلحلة أي عراقيل بيروقراطية أو مالية أو إدارية قد تعيق ذلك، بالتنسيق مع الجهات المعنية كافة.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:11:25.316178+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>الأخبار | وزير الاقتصاد يبحث مع سفير اليابان سبل الاستفادة من التسهيلات الجمركية وتعزيز التعاون الاقتصادي | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/وزير-الاقتصاد-يبحث-مع-سفير-اليابان-سبل-الاستفادة-من-التسهيلات-الجمركية-وتعزيز-التعاون-الاقتصادي</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>وزير الاقتصاد يبحث مع سفير اليابان سبل الاستفادة من التسهيلات الجمركية وتعزيز التعاون الاقتصادي
+*وزير الاقتصاد يبحث مع سفير اليابان سبل الاستفادة من التسهيلات الجمركية وتعزيز التعاون الاقتصادي*
+استقبل وزير الاقتصاد والتجارة د. عامر البساط سعادة سفير دولة اليابان في لبنان السيد كينجي يوكوتا، حيث جرى البحث في سبل تعزيز التعاون الاقتصادي والتجاري بين البلدين، لا سيما في ضوء التسهيلات الاستثنائية التي منحتها اليابان للبنان، بما في ذلك خفض الرسوم الجمركية، وإمكانية الاستفادة منها لزيادة الصادرات اللبنانية.
+كما تناول اللقاء مشاركة لبنان الرسمية في معرض «إكسبو» اليابان، إضافة إلى تأجيل الاجتماع الحضوري الذي كان مقرّراً بين أصحاب الأعمال في البلدين نظراً للظروف الراهنة وتحويله إلى اجتماع افتراضي مرتقب. 
+حول الكاتب: الوزير
+كان لوريم إيبسوم ولايزال المعيار للنص الشكلي منذ القرن الخامس عشر عندما قامت مطبعة مجهولة برص مجموعة من الأحرف بشكل عشوائي أخذتها من نص. لوريم إيبسوم هو ببساطة نص شكلي، بمعنى أن الغاية هي الشكل وليس المحتوى. ويُستخدم في صناعات المطابع ودور النشر. كان لوريم إيبسوم ولايزال المعيار للنص الشكلي منذ القرن الخامس عشر عندما قامت مطبعة مجهولة برص مجموعة من الأحرف بشكل عشوائي أخذتها من نص، لتكوّن كتيّب بمثابة دليل أو مرجع شكلي لهذه الأحرف.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:11:29.538353+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>الأخبار | وزارة الاقتصاد: المخزون الغذائي في لبنان كافٍ لثلاثة أو أربعة أشهر | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/وزارة-الاقتصاد-المخزون-الغذائي-في-لبنان-كافٍ-لثلاثة-أو-أربعة-أشهر</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>الجمهورية اللبنانية 
+وزارة الاقتصاد: المخزون الغذائي في لبنان كافٍ لثلاثة أو أربعة أشهر
+                            الجمعة 10 نيسان 2026
+*وزارة الاقتصاد: المخزون الغذائي في لبنان كافٍ لثلاثة أو أربعة أشهر*
+تؤكد وزارة الاقتصاد والتجارة، أن:
+• التصريح المتداول نقلاً عن مديرة برنامج الأغذية العالمي في لبنان، اقتُطع من سياقه وهو متعلّق فقط بالقرى المحاصرة في الجنوب ولا يعني كل لبنان، وسيتولى المعنيون توضيح هذا الأمر.
+- المخزون الغذائي في لبنان كافٍ لثلاثة أو أربعة أشهر، وسلاسل الإمداد وحركة الاستيراد والتصدير تعمل بشكل طبيعي في المرافئ والمعابر البرية.
+- العمل في المرافئ لا سيما مرفأ بيروت وفي المعابر البرية مستمر بشكل طبيعي، ومن ضمنها معبر المصنع الذي أُعيد فتحه، كما تمّ اعتبار أيام الأعياد والعطل الرسمية أيام عمل عادية لتوفير أقصى قدرة استيعابية. 
+- التنسيق مستمر مع جميع المعنيين في الملف الغذائي ومنهم إدارات المرافئ والمعابر والجمارك اللبنانية والمستوردون وأصحاب السوبرماركت، والعمل مستمر بشكل طبيعي وبأقصى قدرة استيعابية والمخزون الاستراتيجي من الغذاء والمحروقات متوافر.
+حول الكاتب: الوزير
+كان لوريم إيبسوم ولايزال المعيار للنص الشكلي منذ القرن الخامس عشر عندما قامت مطبعة مجهولة برص مجموعة من الأحرف بشكل عشوائي أخذتها من نص. لوريم إيبسوم هو ببساطة نص شكلي، بمعنى أن الغاية هي الشكل وليس المحتوى. ويُستخدم في صناعات المطابع ودور النشر. كان لوريم إيبسوم ولايزال المعيار للنص الشكلي منذ القرن الخامس عشر عندما قامت مطبعة مجهولة برص مجموعة من الأحرف بشكل عشوائي أخذتها من نص، لتكوّن كتيّب بمثابة دليل أو مرجع شكلي لهذه الأحرف.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:11:33.654406+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>الأخبار | تطوّر الأسعار في ظلّ الحرب والإجراءات التنفيذية والرقابية | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/تطوّر-الأسعار-في-ظلّ-الحرب-والإجراءات-التنفيذية-والرقابية</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>تطوّر الأسعار في ظلّ الحرب والإجراءات التنفيذية والرقابية
+وزارة الاقتصاد والتجارة: تطوّر الأسعار في ظلّ الحرب والإجراءات التنفيذية والرقابية
+تتابع وزارة الاقتصاد والتجارة عن كثب تطورات الأسعار في مختلف المناطق اللبنانية، لا سيما وأن معدلات التضخم شهدت ارتفاعاً في مرحلة الحرب. وفي البيان التالي، شرحٌ مفصّل لأسباب التضخم، والإجراءات التنفيذية والرقابية التي تتخذها الوزارة. كما تورد الوزارة في البيانات المرفقة بالأرقام والصور حصيلة رصدها لأسعار 60 سلعة ومدى تغيراتها منذ بدء الحرب إلى اليوم.
+1- أسباب التضخم
+يعود الارتفاع الأخير في الأسعار بشكل أساسي إلى عوامل خارجية وهيكلية.
+أولاً، التصاعد الملحوظ في التضخم المستورد. فقد ارتفعت أسعار الطاقة عالمياً، لا سيما خام برنت (51%) والديزل (86%)، ما أدى إلى زيادة كلفة الإنتاج المحلي. كما ارتفعت تكاليف الشحن البحري وأقساط التأمين على النقل بشكل كبير نتيجة ارتفاع المخاطر في المنطقة، مما انعكس مباشرة على كلفة الاستيراد.
+ثانياً، نظراً لاعتماد لبنان الكبير على الاستيراد، فمن البديهي أن تنعكس هذه الزيادات في الأسعار العالمية على السوق المحلية. ويُعدّ المازوت من أبرز القنوات التي تنتقل عبرها هذه الضغوط، كونه مادة أساسية في مختلف الأنشطة الاقتصادية، من توليد الكهرباء إلى النقل والزراعة والإنتاج الغذائي.
+ثالثاً، أدّت الحرب إلى اضطرابات في سلاسل الإمداد، بما في ذلك صعوبات في النقل الداخلي والتوزيع، مما ساهم في حدوث اختناقات وارتفاعات إضافية في بعض الأسعار.
+رابعاً، في الأسابيع الأخيرة، شهدت قطاعات محدّدة ارتفاعات كبيرة في الأسعار. منها، بشكل خاص أسعار الخضروات التي ارتفعت بشكل حادّ نتيجة عدم التوازن المؤقت بين العرض والطلب. فمن جهة، يعكس هذا الواقع الأضرار الجسيمة التي لحقت بالأراضي الزراعية في الجنوب، وكون الموعد الفعلي لموسم الحصاد لن يبدأ قبل الأشهر المقبلة، إلى جانب الاختلال بين العرض والطلب نتيجة حركة النزوح. وقد لوحظت ديناميكية مماثلة في قطاع اللحوم.
+2- إجراءات وزارة الاقتصاد: تأمين السلع، مراقبة الأسعار، وتطبيق القوانين
+استجابةً لهذه التطورات، اعتمدت الوزارة مقاربة ترتكز على ثلاث أولويات رئيسية:
+أولاً، تأمين توافر السلع. تتمثل أولوية الوزارة في ضمان استمرارية توافر السلع الأساسية في الأسواق. وفي حين أن ارتفاع الأسعار يبقى أمراً غير مرغوب به إطلاقاً، إلا أنه من المهم التأكيد أن عدم عكس الارتفاع في الكلفة الاستيرادية من شأنه أن يُعرّض الأسواق المحليّة لنقص في السلع مما سيُلحق ضرراً كبيراً بالمستهلكين.
+وفي هذا الإطار، تعمل وزارة الاقتصاد والتجارة بشكل وثيق مع المستوردين والموزعين لضمان توافر الكميات اللازمة. تحديداً، يتمّ إعطاء الأولوية لاستيراد السلع الأساسية، كما يتمّ اتخاذ إجراءات محددة في القطاعات التي تشهد نقصاً.
+كما يجري التنسيق مع وزارة الزراعة لتسريع استيراد الخضروات وتسهيل الإجراءات الإدارية والتفتيشية. وقد تم تسهيل استيراد شحنة كبيرة من اللحوم بهدف استقرار الأسعار وتوافر الكميات.
+ثانياً، تعزيز المراقبة والتنسيق. عززت الوزارة أدوات مراقبة الأسعار وفهم ديناميات السوق، وقد تم إطلاق لوحة متابعة للأسعار (Dashboard) تعتمد على ثلاث قواعد بيانات، مما يُتيح رصد تطور الأسعار بشكل دقيق وآني، كما تم تفعيل المجلس الأعلى للأسعار لمتابعة التضخم بشكل تفصيلي والتنسيق مع مختلف الجهات المعنية لاقتراح الحلول العملية والمناسبة، وهو ما تمّ اعتماده في قطاعي الخضار واللحوم على سبيل المثال.
+ثالثاً، مكافحة الزيادات غير المبررة في الأسعار. في حين أن جزءاً كبيراً من ارتفاع الأسعار مبرّر بزيادة الكلفة، فإن الوزارة تتعامل بحزم مع الزيادات غير المبرّرة والممارسات الاستغلالية.
+وفي هذا السياق، كثّفت الوزارة عمليات الرقابة الميدانية على مختلف القطاعات الحيوية، ولا سيما في المناطق التي تشهد ضغطاً متزايداً على السلع الأساسية والمناطق التي تستضيف مراكز الإيواء. ومنذ بداية الحرب في 2 آذار ولغاية 27 منه، نفّذت مديرية حماية المستهلك 1,797 زيارة كشف ميدانية، نتج عنها تسطير أكثر من 75 محضر ضبط بمخالفات متنوعة، وأحالت 116 محضراً إلى القضاء المختصّ.
+وشملت هذه العمليات مراقبة قطاع مستوردي الغاز، حيث تبيّن قيام إحدى الشركات باحتكار عشرة أطنان من الغاز والامتناع عن بيعها للمستهلكين، إضافة إلى متابعة أسواق الخضار بالجملة بالتنسيق مع وزارة الزراعة لضبط الأسعار، وقد سُطّر عدد من محاضر الضبط، لا سيما في ما يتعلق بأسعار البطاطا. كما شملت الرقابة تسليمات مادة الديزل أويل لدى الشركات المستوردة للتأكد من عدم الاحتكار في ظل ارتفاع أسعار النفط الخام عالمياً، وتم رفع تقرير مفصل بهذا الشأن. كذلك جرى التشدد في مراقبة أسعار السلع ونسب الأرباح، خصوصاً المواد الغذائية الأساسية والسلع المرتبطة باحتياجات النازحين، إضافة إلى مراقبة محطات المحروقات، وقطاع المولدات الكهربائية، والأفران، وأسعار الفرشات، وسلامة وجودة وتوافر المواد الغذائية في السوبرماركت والمستودعات ومحال بيع الأغذية الجاهزة.
+هذه الخطوات تأتي تكملة للعمل الاعتيادي لمديرية حماية المستهلك، فمنذ مطلع العام، استجابت المديرية إلى 297 شكوى، ونفّذت 4,901 زيارة كشف، وأصدرت خمسة قرارات تعليق تداول وسطّرت 221 محضر ضبط وأحالت 414 محضراً إلى القضاء المختصّ.
+الجدير ذكره، أن إجراءات الرقابة تتم بالتنسيق مع الأجهزة الأمنية المعنيّة وبالتواصل الدائم مع الجهات القضائية لتعزيز الإجراءات الصارمة كتلف البضائع وإقفال المؤسسات بالشمع الأحمر وإصدار الإنذارات وفقاً للقوانين.
+وتجدّد الوزارة دعوة المواطنين إلى تقديم الشكاوى عبر التطبيق الإلكتروني الخاص بالوزارة (MoET Digital Services)، الذي يشكل أداة أساسية للاستجابة السريعة.
+3- في الخلاصة
+على الرغم من أن الضغوط التضخمية العالمية تنعكس حكماً على الأسعار المحليّة، لكن الوزارة ملتزمة كاملاً بـ:
+• ضمان توافر السلع في الأسواق
+• تعزيز مراقبة الأسعار
+• حماية المستهلك من الممارسات غير المشروعة
+وستواصل الوزارة متابعة التطورات واتخاذ الإجراءات اللازمة بما يضمن استقرار الأسواق وحماية المواطنين.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:11:54.761557+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>الأخبار | البساط التقى وفداً من مزارعي عكار والنائب جيمي جبور | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/البساط-التقى-وفداً-من-مزارعي-عكار-والنائب-جيمي-جبور</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>الجمهورية اللبنانية 
+البساط التقى وفداً من مزارعي عكار والنائب جيمي جبور
+                            الخميس 26 آذار 2026
+*البساط التقى وفداً من مزارعي عكار والنائب جيمي جبور*
+في متابعة للتحديات والصعوبات الهيكلية التي يواجهها مزارعو البطاطا، كغيرهم من المزارعين اللبنانيين، ناقش وزير الاقتصاد والتجارة د. عامر البساط، خلال اجتماع مع وفد من مزارعي البطاطا في عكار يرافقهم النائب جيمي جبور، الحاجة إلى وضع استراتيجية طويلة الأمد توازن بين متطلبات المزارعين، ومصالح المستهلكين، والتزامات لبنان في مجال التجارة الدولية.
+كما تم الاتفاق على ضرورة تعزيز الرقابة والإشراف على حركة التجارة الداخلية للمنتجات الزراعية. وأخيراً، عرضنا مجموعة من الإجراءات العملية التي يمكن للوزارة تنفيذها بهدف فتح أسواق تصديرية أمام المنتجات الزراعية اللبنانية، وتأمين الدعم اللازم للمساعدة التقنية في مجال تعزيز الصادرات. 
+حول الكاتب: الوزير
+كان لوريم إيبسوم ولايزال المعيار للنص الشكلي منذ القرن الخامس عشر عندما قامت مطبعة مجهولة برص مجموعة من الأحرف بشكل عشوائي أخذتها من نص. لوريم إيبسوم هو ببساطة نص شكلي، بمعنى أن الغاية هي الشكل وليس المحتوى. ويُستخدم في صناعات المطابع ودور النشر. كان لوريم إيبسوم ولايزال المعيار للنص الشكلي منذ القرن الخامس عشر عندما قامت مطبعة مجهولة برص مجموعة من الأحرف بشكل عشوائي أخذتها من نص، لتكوّن كتيّب بمثابة دليل أو مرجع شكلي لهذه الأحرف.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:11:58.900504+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>الأخبار | استعرض المجلس الوطني للضمان الارتفاع الحاد الذي شهدته كلفة الرعاية الصحية | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/استعرض-المجلس-الوطني-للضمان-الارتفاع-الحاد-الذي-شهدته-كلفة-الرعاية-الصحية</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>استعرض المجلس الوطني للضمان الارتفاع الحاد الذي شهدته كلفة الرعاية الصحية
+في إطار اجتماعه الدوري، استعرض المجلس الوطني للضمان الارتفاع الحاد الذي شهدته كلفة الرعاية الصحية في الفترة الأخيرة، وما نتج عنه من ضغوط تصاعدية على أقساط التأمين. وقد قرّر المجلس تشكيل لجنة فرعية كُلِّفت بالتنسيق مع وزارة الصحة والنقابات المعنية بالقطاع الصحي، بهدف إعداد توصيات عملية من شأنها الحد من هذه الكلفة.
+كما ناقش المجلس الإجراءات التي تتخذها وزارة الاقتصاد لتنظيم قطاع وساطة التأمين بشكل أفضل، لا سيما القرار الأخير برفع الحد الأدنى لرأس المال المطلوب لشركات الوساطة، إلى جانب العمل الجاري لإعداد (Code of Conduct) جديدة ووضع معايير “الملاءة والملاءمة” (Fit and Proper) الخاصة بالعاملين في هذا القطاع.
+وتناول المجلس كذلك المراجعة الاستراتيجية التي أطلقتها الوزارة، والهادفة إلى تطوير أطر جديدة لإعادة رسملة شركات التأمين، استناداً إلى تقييم المخاطر.
+وفي الختام، استعرض المجلس الجهود المبذولة لمعالجة عدد من القضايا العالقة منذ فترة الأزمة، والعمل على إيجاد حلول مستدامة لها. 
+حول الكاتب: الوزير
+كان لوريم إيبسوم ولايزال المعيار للنص الشكلي منذ القرن الخامس عشر عندما قامت مطبعة مجهولة برص مجموعة من الأحرف بشكل عشوائي أخذتها من نص. لوريم إيبسوم هو ببساطة نص شكلي، بمعنى أن الغاية هي الشكل وليس المحتوى. ويُستخدم في صناعات المطابع ودور النشر. كان لوريم إيبسوم ولايزال المعيار للنص الشكلي منذ القرن الخامس عشر عندما قامت مطبعة مجهولة برص مجموعة من الأحرف بشكل عشوائي أخذتها من نص، لتكوّن كتيّب بمثابة دليل أو مرجع شكلي لهذه الأحرف.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:12:02.765920+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>الأخبار | الأمن الغذائي وتوافر السلع الأساسية في ظل المرحلة الحساسة التي يمر بها البلد | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/الأمن-الغذائي-وتوافر-السلع-الأساسية-في-ظل-المرحلة-الحساسة-التي-يمر-بها-البلد</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>الأمن الغذائي وتوافر السلع الأساسية في ظل المرحلة الحساسة التي يمر بها البلد
+وزير الاقتصاد والتجارة الدكتور عامر البساط من قصر بعبدا:
+- اجتمعت اليوم مع رئيس الجمهورية، ووضعتُه في أجواء الإجراءات التي تتخذها وزارة الاقتصاد لضمان الأمن الغذائي وتوافر السلع الأساسية في ظل المرحلة الحساسة التي يمر بها البلد.
+- أكدتُ أن المخزون من السلع الأساسية متوافر وبمستويات مرتفعة، ولا سيما الطحين والمواد الغذائية والمحروقات، وأن الأمن الغذائي مؤمَّن لعدة أشهر.
+- الاستيراد مستمر ولم يتوقف، وكل ما يُستهلك من المخزون يجري تعويضه بشكل متواصل، كما أن وتيرة التهافت على السلع تراجعت بعد الاطمئنان إلى توافرها.
+- بحثنا في التحديات اللوجستية، فالمخزون موجود، لكن الأهم هو إيصال السلع إلى المستهلك، وهناك تنسيق قائم بين الوزارات والقوى الأمنية لضمان ذلك.
+- هناك ارتفاع في بعض الأسعار نتيجة الأوضاع الأمنية وارتفاع الأسعار عالمياً، خصوصاً في المحروقات، لكننا لن نسمح بأي استغلال للظروف أو تضخم غير مبرر.
+- فرق المراقبة تكثّف جولاتها الميدانية بالتعاون مع القوى الأمنية والقضاء، وقد اتُّخذت إجراءات بحق مخالفين، وأُقفلت محطات وقود ومتاجر تلاعبت بالأسعار.
+- أما بالنسبة إلى أسعار المحروقات، فهي تُحدَّد وفق آلية تعتمد على معدل الأسعار العالمية في الأيام الأخيرة، وأي انخفاض خارجي سينعكس تلقائياً على الأسعار في لبنان.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:12:07.129276+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>الأخبار | ضمان الأمن الغذائي وتوافر السلع الأساسية في ظلّ الظروف الراهنة | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/ضمان-الأمن-الغذائي-وتوافر-السلع-الأساسية-في-ظلّ-الظروف-الراهنة</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ضمان الأمن الغذائي وتوافر السلع الأساسية في ظلّ الظروف الراهنة
+*مذكرة صادرة عن وزارة الاقتصاد والتجارة*
+*بشأن ضمان الأمن الغذائي وتوافر السلع الأساسية في ظلّ الظروف الراهنة*
+بيروت - في 8 آذار 2026
+في ضوء التطورات الأخيرة والتحديات الاقتصادية، وضعت وزارة الاقتصاد والتجارة خطة استباقية لضمان الأمن الغذائي وتوافر السلع الأساسية في مختلف المناطق اللبنانية، والحفاظ على انسيابية سلاسل الإمداد ومنع أي اضطرابات في الأسواق أو احتكار أو تلاعب بالأسعار أو استغلال للظروف الراهنة،
+وفي هذا الإطار، تعمل الوزارة على تنفيذ الإجراءات التالية:
+*أولاً: الاستفادة من المخزون الاستراتيجي المتوافر*
+تشير المعطيات المتوافرة لدى الوزارة إلى أن المخزون الحالي من السلع الأساسية، بما فيها المواد الغذائية والقمح والمحروقات، كافٍ لتغطية أشهر عدة من الاستهلاك المحلي.
+وتتابع الوزارة مستويات المخزون يومياً بالتنسيق مع المستوردين والموردين، لضمان استمرار توزيع السلع ووصولها إلى مختلف المناطق ونقاط البيع من دون انقطاع أو ممارسات احتكارية.
+*ثانياً: تأمين شحنات إضافية بشكل استباقي*
+بالتوازي مع متابعة المخزون، تعمل الوزارة على ضمان استمرار تدفق الإمدادات إلى لبنان بانتظام.
+ولهذه الغاية تقوم الوزارة بما يلي:
+• تحديد الاحتياجات الوطنية من السلع الأساسية للأشهر المقبلة.
+• حثّ المستوردين على استيراد كميات إضافية مبكراً وعدم انتظار تقلبات الأسعار العالمية، إذ إن أولوية المرحلة هي ضمان توافر السلع وحماية الأمن الغذائي.
+• التنسيق مع شركات الشحن والموردين الدوليين لتسريع وصول الشحنات الجديدة إلى مرفأ بيروت وسائر المرافئ، إضافة إلى المعابر البرية.
+*ثالثاً: ضمان انسيابية سلسلة الإمداد*
+تعمل الوزارة بالتنسيق مع الإدارات والجهات المعنية على تأمين استمرارية سلسلة إمداد السلع الأساسية من لحظة وصولها إلى لبنان وحتى وصولها إلى المستهلك.
+ويشمل ذلك:
+• إعطاء الأولوية في المرافئ لتفريغ السفن المحمّلة بالمواد الغذائية والسلع الأساسية.
+• التنسيق مع إدارة مرفأ بيروت والجمارك وسائر الإدارات المعنية لتسهيل وتسريع الإجراءات اللوجستية والإدارية، لتخليص البضائع وإخراجها من المرافئ سريعاً ومن دون تأخير.
+• تسهيل انتقال السلع من مراكز التخزين إلى الأسواق ونقاط البيع في مختلف المناطق.
+• متابعة ملف القمح يومياً لضمان تسليمه إلى المطاحن وتوافر الطحين للأفران في الوقت المناسب.
+• منح الأولوية في توزيع المازوت للمؤسسات الحيوية، ولا سيما المستشفيات والأفران ومراكز الإنتاج، وفق لوائح جرى إعدادها لحاجاتها الشهرية.
+*رابعاً: مراقبة الأسعار ومنع التضخم غير المبرّر*
+في ظل الارتفاعات في بعض الأسعار العالمية، طوّرت الوزارة قاعدة بيانات ديناميكية لمراقبة أسعار المحروقات والسلع الأساسية في الأسواق اللبنانية بشكل شبه فوري.
+وتهدف هذه المنظومة إلى رصد أي ارتفاعات غير مبرّرة في الأسعار والتدخّل السريع لمعالجتها ومنع أي استغلال للظروف الراهنة لتحقيق أرباح غير مشروعة على حساب المواطنين.
+كما تعمل الوزارة على تفعيل المجلس الوطني لسياسة الأسعار عملاً بالصلاحيات المخولة لوزير الاقتصاد والتجارة بصفته رئيساً للمجلس.
+*خامساً: تشديد الرقابة عبر مديرية حماية المستهلك*
+توازياً، كثّفت مديرية حماية المستهلك جولاتها الرقابية الميدانية على الأسواق والمستودعات ونقاط البيع في مختلف المناطق.
+وتقوم بتسطير محاضر ضبط بحق المخالفين وإحالتهم إلى القضاء المختص، ولن تتردد الوزارة في إقفال المؤسسات المخالفة بالشمع الأحمر عند الاقتضاء، خصوصاً في حالات الاحتكار أو التلاعب بالأسعار أو الامتناع عن البيع.
+*أخيراً،* تدعو الوزارة المواطنين إلى المساهمة في حماية الأسواق عبر الإبلاغ عن أي مخالفات عبر تطبيقها الإلكتروني (MoET Digital Services). كما تدعو المستوردين والتجار إلى تقديم معاملاتهم عبر المنصات الإلكترونية المعتمدة، لتسريع إنجازها وتسهيل الإجراءات الإدارية وضمان الشفافية.
+في هذه المرحلة الدقيقة، تؤكد الوزارة التزامها بالمتابعة اليومية والتنسيق مع الإدارات المعنية والقطاع الخاص والشركاء الدوليين، واتخاذها جميع التدابير اللازمة لحماية الأمن الغذائي واستقرار السوق وصون مصلحة المواطنين.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:12:15.694243+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>الأخبار | وزير الاقتصاد يدعو المجلس الوطني لسياسة الأسعار لاجتماع استثنائي الجمعة | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/وزير-الاقتصاد-يدعو-المجلس-الوطني-لسياسة-الأسعار-لاجتماع-استثنائي-الجمعة</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>الجمهورية اللبنانية 
+وزير الاقتصاد يدعو المجلس الوطني لسياسة الأسعار لاجتماع استثنائي الجمعة
+                            الخميس 05 آذار 2026
+*وزير الاقتصاد يدعو المجلس الوطني لسياسة الأسعار لاجتماع استثنائي الجمعة*
+دعا وزير الاقتصاد والتجارة الدكتور عامر البساط إلى عقد اجتماع للمجلس الوطني لسياسة الأسعار في مقر الوزارة عند الساعة العاشرة من صباح الجمعة 6 آذار 2026، لبحث التطورات الأخيرة في حركة الأسعار في الأسواق اللبنانية في ظل الظروف الراهنة.
+وجاءت الدعوة في ضوء معطيات ميدانية تشير إلى ارتفاعات غير مبررة في أسعار عدد من المواد الغذائية والاستهلاكية، مما يشكّل عبئاً متزايداً على المواطنين، وذلك عملاً بالصلاحيات المخولة لوزير الاقتصاد والتجارة بصفته رئيساً للمجلس.
+وسيُخصص الاجتماع لعرض المعطيات الميدانية حول تطورات الأسعار خلال الأسابيع الأخيرة وتحديد القطاعات والسلع الأكثر تضرراً، إضافة إلى تحليل العوامل المؤثرة في ارتفاع الأسعار، بما فيها أوضاع سلاسل التوريد في مختلف حلقات التوزيع.
+كما سيعمل المجلس على صياغة توصيات عملية قابلة للتطبيق بهدف حماية القدرة الشرائية للمواطنين لا سيما في هذه الظروف.
+حول الكاتب: الوزير
+كان لوريم إيبسوم ولايزال المعيار للنص الشكلي منذ القرن الخامس عشر عندما قامت مطبعة مجهولة برص مجموعة من الأحرف بشكل عشوائي أخذتها من نص. لوريم إيبسوم هو ببساطة نص شكلي، بمعنى أن الغاية هي الشكل وليس المحتوى. ويُستخدم في صناعات المطابع ودور النشر. كان لوريم إيبسوم ولايزال المعيار للنص الشكلي منذ القرن الخامس عشر عندما قامت مطبعة مجهولة برص مجموعة من الأحرف بشكل عشوائي أخذتها من نص، لتكوّن كتيّب بمثابة دليل أو مرجع شكلي لهذه الأحرف.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:12:19.868905+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>الأخبار | اجتماع هام لوزيري الاقتصاد والزراعة بشأن أسعار المواد الغذائية مع ممثلي النقابات لتباحث المطالب والحلول | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/اجتماع-هام-لوزيري-الاقتصاد-والزراعة-بشأن-أسعار-المواد-الغذائية-مع-ممثلي-النقابات-لتباحث-المطالب-والحلول</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>اجتماع هام لوزيري الاقتصاد والزراعة بشأن أسعار المواد الغذائية مع ممثلي النقابات لتباحث المطالب والحلول
+*اجتماع هام لوزيري الاقتصاد والزراعة بشأن أسعار المواد الغذائية مع ممثلي النقابات لتباحث المطالب والحلول*
+عقد وزيرا الاقتصاد والتجارة عامر البساط والزراعة نزار هاني اجتماعاً موسعاً في وزارة الاقتصاد، بحضور المديرين العامَّين في الوزارتين ومسؤولي الرقابة، وممثلين عن النقابات الغذائية والزراعية والأسواق المركزية، لبحث ملف أسعار المواد الغذائية والتحديات التي تواجه القطاعات.
+وأكد البساط على حساسيّة الملف المعيشي ومنحه أولوية قصوى، مشيراً إلى تكثيف الإجراءات الرقابية وعقد لقاءات متتالية مع المعنيين لضبط الأسعار ومنع أي زيادات غير مبررة. وكشف أن مديرية حماية المستهلك نفذت خلال الأسابيع الستة الأولى من عام 2026 نحو 1928 زيارة كشف وحررت أكثر من 100 محضر ضبط، فيما سُجل في عام 2025 أكثر من 32 ألف زيارة و1454 محضر ضبط، توزعت بين مخالفات تتعلق بالمولدات وسلامة الغذاء والأسعار والأوزان.
+وشدد البساط على ثلاثة مسارات: التشدد في الرقابة وتطبيق القوانين من دون تهاون، مواصلة الجولات الميدانية ومنع أي تلاعب بالأسعار، وتعزيز الشراكة مع القطاع الخاص لحماية الاستقرار الاجتماعي، ولا سيما عبر مبادرة “سوا بالصيام” بالتعاون مع أصحاب السوبرماركت والمستوردين، لتخفيف الأعباء خلال شهر رمضان والصوم الكبير.
+من جهته، اعتبر وزير الزراعة أن الخلل الأساسي يكمن في سلسلة التوريد لا في الإنتاج، لافتاً إلى الفوارق الكبيرة بين أسعار المنتجات في أرض المزرعة وأسعارها في أسواق المفرق، ما يظلم المزارع ويُرهق المستهلك في آن واحد. وأشار إلى أن المشكلة تمتد إلى اللحوم والدواجن، حيث تتضخم الهوامش بين باب المزرعة ونقطة البيع.
+ودعا هاني إلى إعادة التوازن إلى السوق عبر ضبط آليات التسعير، تقليص عدد الوسطاء، تحقيق شفافية كاملة في تحديد الأسعار، ووضع سقوف منطقية لهوامش الربح، مؤكداً أن حماية المزارع والمستهلك مسؤولية وطنية واحدة لضمان الأمن الغذائي والاستقرار الاجتماعي.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:12:23.870825+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>الأخبار | وزارة الاقتصاد: لا تهاون في ضبط الأسعار وحماية المستهلك | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/وزارة-الاقتصاد-لا-تهاون-في-ضبط-الأسعار-وحماية-المستهلك</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>وزارة الاقتصاد: لا تهاون في ضبط الأسعار وحماية المستهلك
+*وزارة الاقتصاد: لا تهاون في ضبط الأسعار وحماية المستهلك*
+تؤكد وزارة الاقتصاد والتجارة استمرار المتابعة اليومية لواقع الأسواق، من خلال الكشوفات الدورية التي تنفذها مديرية حماية المستهلك على مختلف الأراضي اللبنانية.
+وفي ضوء الإجراءات الحكومية الأخيرة، تشدد الوزارة على تكثيف حملات التفتيش والرقابة خلال المرحلة المقبلة، ولن تتهاون في ضبط أي مخالفات أو زيادات غير مبررة في الأسعار، لما تشكله من إساءة للمستهلك ومساس باستقرار السوق. وتؤكد الوزارة أن أي استغلال أو تجاوزات سعرية هو أمر غير مقبول وسيواجه بالإجراءات القانونية اللازمة.
+وتأتي هذه الحملات استكمالاً لسلسلة الاجتماعات التي عقدها معالي وزير الاقتصاد والتجارة مع نقابتي السوبرماركت والأفران، حيث تم التأكيد على التزام المعنيين بعدم رفع الأسعار وتحمل مسؤولياتهم في هذه المرحلة.
+كما تذكّر الوزارة بمبادرة "سوا بالصيام"، التي التزمت في إطارها 27 سلسلة سوبرماركت بتقديم حسومات لا تقل عن 15% على 21 سلعة أساسية، في خطوة تهدف إلى تخفيف الأعباء عن المواطنين وتعزيز الاستقرار الاجتماعي.
+وستستأنف الوزارة تباعاً نشر التقارير الدورية الصادرة عن مديرية حماية المستهلك، تعزيزاً للشفافية وإطلاعاً للرأي العام.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:12:27.974962+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>الأخبار | البساط يبحث مع حبيب دور مصرف الإسكان ودعم القروض الإسكانية | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/البساط-يبحث-مع-حبيب-دور-مصرف-الإسكان-ودعم-القروض-الإسكانية</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>البساط يبحث مع حبيب دور مصرف الإسكان ودعم القروض الإسكانية
+*البساط يبحث مع حبيب دور مصرف الإسكان ودعم القروض الإسكانية*
+التقى وزير الاقتصاد والتجارة الدكتور عامر البساط، برئيس مجلس الإدارة المدير العام لمصرف الإسكان أنطوان حبيب، واطّلع منه على مشاريع مصرف الإسكان وحركة القروض الإسكانية المخصّصة لذوي الدخل المحدود والمتوسط وذوي الاحتياجات الخاصة، إضافةً إلى الجهود المبذولة لتأمين ديمومة هذه القروض عبر قروض مدعومة من الصناديق العربية.
+وأثنى البساط على مشاريع مصرف الإسكان ودوره في خدمة المواطنين وضمان الحق بالسكن وتعزيز الاستقرار الاجتماعي. 
+حول الكاتب: الوزير
+كان لوريم إيبسوم ولايزال المعيار للنص الشكلي منذ القرن الخامس عشر عندما قامت مطبعة مجهولة برص مجموعة من الأحرف بشكل عشوائي أخذتها من نص. لوريم إيبسوم هو ببساطة نص شكلي، بمعنى أن الغاية هي الشكل وليس المحتوى. ويُستخدم في صناعات المطابع ودور النشر. كان لوريم إيبسوم ولايزال المعيار للنص الشكلي منذ القرن الخامس عشر عندما قامت مطبعة مجهولة برص مجموعة من الأحرف بشكل عشوائي أخذتها من نص، لتكوّن كتيّب بمثابة دليل أو مرجع شكلي لهذه الأحرف.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:13:10.825738+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>الأخبار | الوزير البساط يجتمع بوفد من صندوق النقد الدولي | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/الوزير-البساط-يجتمع-بوفد-من-صندوق-النقد-الدولي</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>الوزير البساط يجتمع بوفد من صندوق النقد الدولي
+الوزير البساط يجتمع بوفد من صندوق النقد الدولي
+*الوزير البساط يجتمع بوفد من صندوق النقد الدولي*
+اجتمع وزير الاقتصاد والتجارة، الدكتور عامر البساط، بوفد من صندوق النقد الدولي برئاسة إرنستو راميريز ريغو، حيث جرى بحث ملاحظات الصندوق على مشروع قانون معالجة أوضاع المصارف، إضافة إلى مشروع قانون الانتظام المالي واسترداد الودائع.
+كما تناول البحث الإصلاحات الهيكلية، والتأكيد على تصميم لبنان على التوصل إلى اتفاق حول برنامج مع الصندوق، بما يتوافق مع سياسات الحكومة اللبنانية، وبما يراعي توازناً مدروساً مع المتطلبات الاجتماعية والاقتصادية، ويحفظ الاستقرارين المالي والنقدي. 
+حول الكاتب: الوزير
+كان لوريم إيبسوم ولايزال المعيار للنص الشكلي منذ القرن الخامس عشر عندما قامت مطبعة مجهولة برص مجموعة من الأحرف بشكل عشوائي أخذتها من نص. لوريم إيبسوم هو ببساطة نص شكلي، بمعنى أن الغاية هي الشكل وليس المحتوى. ويُستخدم في صناعات المطابع ودور النشر. كان لوريم إيبسوم ولايزال المعيار للنص الشكلي منذ القرن الخامس عشر عندما قامت مطبعة مجهولة برص مجموعة من الأحرف بشكل عشوائي أخذتها من نص، لتكوّن كتيّب بمثابة دليل أو مرجع شكلي لهذه الأحرف.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:13:14.489947+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>الأخبار | وزير الاقتصاد عامر البساط: غرفة التجارة البريطانية - اللبنانية منصّة لمضاعفة الصادرات والاستثمار | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/وزير-الاقتصاد-عامر-البساط-غرفة-التجارة-البريطانية---اللبنانية-منصّة-لمضاعفة-الصادرات-والاستثمار</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>وزير الاقتصاد عامر البساط: غرفة التجارة البريطانية - اللبنانية منصّة لمضاعفة الصادرات والاستثمار
+*وزير الاقتصاد عامر البساط: غرفة التجارة البريطانية - اللبنانية منصّة لمضاعفة الصادرات والاستثمار*
+أعلن وزير الاقتصاد والتجارة الدكتور عامر البساط أنّ إطلاق غرفة التجارة البريطانية – اللبنانية يشكّل خطوة استراتيجية لتعزيز العلاقات الاقتصادية بين لبنان والمملكة المتحدة، ويمثّل منصّة أساسية لمضاعفة الصادرات والاستثمارات بين البلدين.
+وجاء موقف الوزير البساط خلال حفل إطلاق غرفة التجارة البريطانية – اللبنانية (British Lebanese Chamber of Commerce)، الذي أقامه السفير البريطاني هايمش كاوِل في مقرّ إقامته أمس، بحضور عدد من روّاد ورجال الأعمال اللبنانيين وأعضاء محتملين في الغرفة.
+وأشار الوزير البساط إلى أنّ "غرفة التجارة البريطانية – اللبنانية ستشكّل منصّة لزيادة الصادرات والاستثمار بين بلدينا، وجزءاً مهماً من مسار انتقال لبنان، كاقتصاد وبلد، من مرحلة التعافي إلى الانخراط مجدداً في مسار الازدهار، من خلال تعزيز التجارة والاستثمار وبناء شراكات متينة مع الأسواق الدولية".
+وكان السفير البريطاني هايمش كاوِل قد اعتبر أنّ إطلاق الغرفة يشكّل خطوة أساسية لتعزيز الشراكات التجارية وخلق فرص جديدة للشركات في البلدين، فيما أكّد رئيس الغرفة فريد شديد أنّ دورها يتمثّل في ربط المبادرات اللبنانية بالمعايير البريطانية، وتمكين الشركات البريطانية من مقاربة السوق اللبنانية برؤية واضحة وطويلة الأمد.
+وتُعدّ غرفة التجارة البريطانية – اللبنانية منظمة رسمية غير ربحية، وعضواً في الشبكة الدولية لغرف التجارة البريطانية التي تضم أكثر من 75 غرفة حول العالم، وتهدف، بدعم من السفارة البريطانية في بيروت، إلى أن تكون جسراً استراتيجياً بين مجتمعي الأعمال اللبناني والبريطاني عبر تسهيل الشراكات، وتوفير الخبرات والأسواق.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:13:18.485025+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Ministry_of_Economy_and_Trade.xlsx
+++ b/Ministry_of_Economy_and_Trade.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2316,6 +2316,38 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>الأخبار | تواصل وزارة الاقتصاد والتجارة رقابتها على الأسواق وملاحقة المخالفات | لبنان - وزارة الأقتصاد والتجارة</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://economy.gov.lb/ar/news/تواصل-وزارة-الاقتصاد-والتجارة-رقابتها-على-الأسواق-وملاحقة-المخالفات</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>تواصل وزارة الاقتصاد والتجارة رقابتها على الأسواق وملاحقة المخالفات
+انطلاقاً من إدراكها لحجم الأزمة وأثرها على معيشة اللبنانيين، تواصل وزارة الاقتصاد والتجارة رقابتها على الأسواق وملاحقة المخالفات. وفي هذا السياق، جال الوزير الدكتور عامر البساط على عدد من المؤسسات والمولّدات في عدة مناطق من بيروت برفقة مراقبي مديرية حماية المستهلك، وعقب الجولة، عقد الوزير البساط مؤتمراً صحافياً أكد فيه على أن الغلاء يطال الجميع وأن المواطن الذي تثقله الفواتير يريد نتائج يلمسها.
+وقال البساط أن ارتفاع كلفة المازوت والنقل، بفعل الضغوط الخارجية، ينعكس على الأسعار. لكن زيادة الكلفة لا تبرّر مضاعفة الأسعار، ولا تعفي المؤسسات من الالتزام بالقانون.
+وعرض إجراءات اتُّخذت خلال الفترة الماضية، شملت توقيف صاحب مولّد إثر مخالفات جسيمة ومصادرة مولّده وتسليمه إلى بلدية بيروت لتشغيله، ووقف تداول منتجات غذائية غير مطابقة للمواصفات، وإقفال محطات محروقات مخالفة بالتعاون مع الوزارات المعنية.
+وتأتي هذه الإجراءات ضمن عمل رقابي شمل نحو 20 ألف كشف ومتابعة أكثر من ألفَي شكوى منذ بداية العام، بفريق يضمّ نحو 70 مراقباً في مختلف المناطق اللبنانية. وفي ملف المولدات، شدّد البساط على إلزامية تركيب العدادات واحترام التعرفة الرسمية.
+ولمواجهة أسباب الغلاء أيضاً، شدّد البساط على تفعيل هيئة المنافسة ومراقبة هوامش الربح، وإقرار قانون حماية المستهلك الجديد. ودعا المواطنين إلى تقديم شكاواهم عبر تطبيق *MoET Digital Services*، مؤكداً أن مسؤولية الوزارة هي متابعتها واتخاذ الإجراءات بحق المخالفين.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:50:35.699690+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
